--- a/outputs/NSW_mlf.xlsx
+++ b/outputs/NSW_mlf.xlsx
@@ -4007,8 +4007,10 @@
           <t>HUNTER1</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
-        <v/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>HUNTER</t>
+        </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
@@ -4895,8 +4897,10 @@
           <t>LIDDNL1</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n">
-        <v/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>LIDDELL</t>
+        </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
@@ -5599,8 +5603,10 @@
           <t>MPNL1</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n">
-        <v/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
@@ -5903,8 +5909,10 @@
           <t>TUMUT1-2</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n">
-        <v/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT1</t>
+        </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
@@ -5959,8 +5967,10 @@
           <t>TUMUT1-3</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n">
-        <v/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT1</t>
+        </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
@@ -6015,8 +6025,10 @@
           <t>TUMUT1-1</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n">
-        <v/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT1</t>
+        </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
@@ -6071,8 +6083,10 @@
           <t>TUMUT1-4</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n">
-        <v/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT1</t>
+        </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
@@ -6127,8 +6141,10 @@
           <t>TUMUT2-3</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n">
-        <v/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT2</t>
+        </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
@@ -6183,8 +6199,10 @@
           <t>TUMUT2-1</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n">
-        <v/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT2</t>
+        </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
@@ -6239,8 +6257,10 @@
           <t>TUMUT2-2</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n">
-        <v/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT2</t>
+        </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
@@ -6295,8 +6315,10 @@
           <t>TUMUT2-4</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n">
-        <v/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT2</t>
+        </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
@@ -7021,8 +7043,10 @@
           <t>VPNL1</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n">
-        <v/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>VP</t>
+        </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
@@ -7201,8 +7225,10 @@
           <t>TUMT3NL3</t>
         </is>
       </c>
-      <c r="B120" s="2" t="n">
-        <v/>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY1</t>
+        </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
@@ -7257,8 +7283,10 @@
           <t>TUMT3NL2</t>
         </is>
       </c>
-      <c r="B121" s="2" t="n">
-        <v/>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY1</t>
+        </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
@@ -7313,8 +7341,10 @@
           <t>TUMT3NL1</t>
         </is>
       </c>
-      <c r="B122" s="2" t="n">
-        <v/>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY1</t>
+        </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
@@ -7431,8 +7461,10 @@
           <t>ERNL1</t>
         </is>
       </c>
-      <c r="B124" s="2" t="n">
-        <v/>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ERARING</t>
+        </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
@@ -8447,8 +8479,10 @@
           <t>DG_NSW1</t>
         </is>
       </c>
-      <c r="B141" s="2" t="n">
-        <v/>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>DG_NSW1</t>
+        </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
@@ -8503,8 +8537,10 @@
           <t>STGEORG1</t>
         </is>
       </c>
-      <c r="B142" s="2" t="n">
-        <v/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>STGEORGE</t>
+        </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
@@ -8977,8 +9013,10 @@
           <t>GUTHNL1</t>
         </is>
       </c>
-      <c r="B150" s="2" t="n">
-        <v/>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY3</t>
+        </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
@@ -9033,8 +9071,10 @@
           <t>TUMUT3-3</t>
         </is>
       </c>
-      <c r="B151" s="2" t="n">
-        <v/>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT3</t>
+        </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
@@ -9089,8 +9129,10 @@
           <t>TUMUT3-2</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n">
-        <v/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT3</t>
+        </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
@@ -9145,8 +9187,10 @@
           <t>TUMUT3-1</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n">
-        <v/>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT3</t>
+        </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
@@ -9201,8 +9245,10 @@
           <t>TUMUT3-6</t>
         </is>
       </c>
-      <c r="B154" s="2" t="n">
-        <v/>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT3</t>
+        </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
@@ -9257,8 +9303,10 @@
           <t>TUMUT3-5</t>
         </is>
       </c>
-      <c r="B155" s="2" t="n">
-        <v/>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT3</t>
+        </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
@@ -9313,8 +9361,10 @@
           <t>TUMUT3-4</t>
         </is>
       </c>
-      <c r="B156" s="2" t="n">
-        <v/>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>TUMUT3</t>
+        </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
@@ -9369,8 +9419,10 @@
           <t>REDBANK1</t>
         </is>
       </c>
-      <c r="B157" s="2" t="n">
-        <v/>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>REDBANK1</t>
+        </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
@@ -9399,8 +9451,10 @@
           <t>HEZ</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n">
-        <v/>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>HEZ</t>
+        </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
@@ -9431,8 +9485,10 @@
           <t>BANKSPT1</t>
         </is>
       </c>
-      <c r="B159" s="2" t="n">
-        <v/>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>BANKSPT</t>
+        </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
@@ -9465,8 +9521,10 @@
           <t>AWABAREF</t>
         </is>
       </c>
-      <c r="B160" s="2" t="n">
-        <v/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>AWABAREF</t>
+        </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
@@ -9501,8 +9559,10 @@
           <t>NINEWIL1</t>
         </is>
       </c>
-      <c r="B161" s="2" t="n">
-        <v/>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>NINEWIL</t>
+        </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
@@ -9541,8 +9601,10 @@
           <t>WOYWOY1</t>
         </is>
       </c>
-      <c r="B162" s="2" t="n">
-        <v/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>WOYWOY</t>
+        </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
@@ -9583,8 +9645,10 @@
           <t>TERALBA</t>
         </is>
       </c>
-      <c r="B163" s="2" t="n">
-        <v/>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>TERALBA</t>
+        </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
@@ -9625,8 +9689,10 @@
           <t>KINCUM1</t>
         </is>
       </c>
-      <c r="B164" s="2" t="n">
-        <v/>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>KINCUMB</t>
+        </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
@@ -9667,8 +9733,10 @@
           <t>LD03</t>
         </is>
       </c>
-      <c r="B165" s="2" t="n">
-        <v/>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>LIDDELL</t>
+        </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
@@ -9709,8 +9777,10 @@
           <t>HVGTS</t>
         </is>
       </c>
-      <c r="B166" s="2" t="n">
-        <v/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>HUNTVGT</t>
+        </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
@@ -9751,8 +9821,10 @@
           <t>AGLNOW1</t>
         </is>
       </c>
-      <c r="B167" s="2" t="n">
-        <v/>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>AGLNOW1</t>
+        </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
@@ -9793,8 +9865,10 @@
           <t>AGLSITA1</t>
         </is>
       </c>
-      <c r="B168" s="2" t="n">
-        <v/>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>AGLSITA</t>
+        </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
@@ -9833,8 +9907,10 @@
           <t>LD01</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n">
-        <v/>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>LIDDELL</t>
+        </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
@@ -9877,8 +9953,10 @@
           <t>LD02</t>
         </is>
       </c>
-      <c r="B170" s="2" t="n">
-        <v/>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>LIDDELL</t>
+        </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
@@ -9921,8 +9999,10 @@
           <t>LD04</t>
         </is>
       </c>
-      <c r="B171" s="2" t="n">
-        <v/>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>LIDDELL</t>
+        </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
@@ -9965,8 +10045,10 @@
           <t>WALGRVG1</t>
         </is>
       </c>
-      <c r="B172" s="2" t="n">
-        <v/>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>WALGBESS</t>
+        </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
@@ -10001,8 +10083,10 @@
           <t>DPNTBG1</t>
         </is>
       </c>
-      <c r="B173" s="2" t="n">
-        <v/>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>DPNTBESS</t>
+        </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
@@ -10035,8 +10119,10 @@
           <t>BHBG1</t>
         </is>
       </c>
-      <c r="B174" s="2" t="n">
-        <v/>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>BHBESS</t>
+        </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
@@ -10067,8 +10153,10 @@
           <t>MLLFGEF1</t>
         </is>
       </c>
-      <c r="B175" s="2" t="n">
-        <v/>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>MLLFGEF</t>
+        </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
@@ -10103,8 +10191,10 @@
           <t>QBYNBG1</t>
         </is>
       </c>
-      <c r="B176" s="2" t="n">
-        <v/>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>QBYNBESS</t>
+        </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
@@ -10137,8 +10227,10 @@
           <t>RESS1G</t>
         </is>
       </c>
-      <c r="B177" s="2" t="n">
-        <v/>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>RESS1</t>
+        </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
@@ -10171,8 +10263,10 @@
           <t>RIVNBG2</t>
         </is>
       </c>
-      <c r="B178" s="2" t="n">
-        <v/>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>RESS2</t>
+        </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
@@ -10205,8 +10299,10 @@
           <t>CAPBES1G</t>
         </is>
       </c>
-      <c r="B179" s="2" t="n">
-        <v/>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>CBESS</t>
+        </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
@@ -10237,8 +10333,10 @@
           <t>WESTCBT1</t>
         </is>
       </c>
-      <c r="B180" s="2" t="n">
-        <v/>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>WESTCBT</t>
+        </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
@@ -18182,8 +18280,10 @@
           <t>TUMT3NL3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY1</t>
+        </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
@@ -18207,8 +18307,10 @@
           <t>TUMT3NL2</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
-        <v/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY1</t>
+        </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
@@ -18232,8 +18334,10 @@
           <t>TUMT3NL1</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SNOWY1</t>
+        </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>

--- a/outputs/NSW_mlf.xlsx
+++ b/outputs/NSW_mlf.xlsx
@@ -4009,13 +4009,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>HUNTER</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Hunter Power Station</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>375</v>
+      </c>
       <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr"/>
@@ -4899,13 +4903,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>LIDDELL</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
+          <t>Liddell Power Station</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E81" s="4" t="n">
         <v>0.9676</v>
       </c>
@@ -5605,13 +5613,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
+          <t>MT PIPER POWER STATION</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E93" s="4" t="n">
         <v>0.9744</v>
       </c>
@@ -5914,10 +5926,10 @@
           <t>TUMUT1</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="3" t="n">
+        <v>82</v>
+      </c>
       <c r="E98" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -5972,10 +5984,10 @@
           <t>TUMUT1</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="3" t="n">
+        <v>82</v>
+      </c>
       <c r="E99" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -6030,10 +6042,10 @@
           <t>TUMUT1</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="3" t="n">
+        <v>82</v>
+      </c>
       <c r="E100" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -6088,10 +6100,10 @@
           <t>TUMUT1</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="3" t="n">
+        <v>82</v>
+      </c>
       <c r="E101" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -6146,10 +6158,10 @@
           <t>TUMUT2</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="E102" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -6204,10 +6216,10 @@
           <t>TUMUT2</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="E103" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -6262,10 +6274,10 @@
           <t>TUMUT2</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="E104" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -6320,10 +6332,10 @@
           <t>TUMUT2</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="E105" s="4" t="n">
         <v>0.9768</v>
       </c>
@@ -7045,13 +7057,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>VP</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
+          <t>Vales Point "B" Power Station</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E117" s="4" t="n">
         <v>0.9877</v>
       </c>
@@ -7227,13 +7243,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>SNOWY1</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="inlineStr"/>
+          <t>Tumut 3 Power Station</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E120" s="4" t="n">
         <v>0.991</v>
       </c>
@@ -7285,13 +7305,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>SNOWY1</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
+          <t>Tumut 3 Power Station</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E121" s="4" t="n">
         <v>0.991</v>
       </c>
@@ -7343,13 +7367,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>SNOWY1</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="inlineStr"/>
+          <t>Tumut 3 Power Station</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E122" s="4" t="n">
         <v>0.991</v>
       </c>
@@ -7463,13 +7491,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>ERARING</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="inlineStr"/>
+          <t>ERARING POWER STATION</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E124" s="4" t="n">
         <v>0.9867</v>
       </c>
@@ -8481,13 +8513,13 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>DG_NSW1</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>NSW1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr"/>
+      <c r="D141" s="3" t="n">
+        <v>3000</v>
+      </c>
       <c r="E141" s="4" t="n">
         <v>1</v>
       </c>
@@ -8539,13 +8571,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>STGEORGE</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
+          <t>St George Leagues Plant</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E142" s="4" t="n">
         <v>1.0059</v>
       </c>
@@ -9015,13 +9051,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>SNOWY3</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
+          <t>Guthega Power Station</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E150" s="4" t="n">
         <v>0.9549</v>
       </c>
@@ -9076,10 +9116,10 @@
           <t>TUMUT3</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E151" s="4" t="n">
         <v>1.0092</v>
       </c>
@@ -9134,10 +9174,10 @@
           <t>TUMUT3</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr"/>
+      <c r="D152" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E152" s="4" t="n">
         <v>1.0092</v>
       </c>
@@ -9192,10 +9232,10 @@
           <t>TUMUT3</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr"/>
+      <c r="D153" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E153" s="4" t="n">
         <v>1.0092</v>
       </c>
@@ -9250,10 +9290,10 @@
           <t>TUMUT3</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E154" s="4" t="n">
         <v>1.0092</v>
       </c>
@@ -9308,10 +9348,10 @@
           <t>TUMUT3</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr"/>
+      <c r="D155" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E155" s="4" t="n">
         <v>1.0092</v>
       </c>
@@ -9366,10 +9406,10 @@
           <t>TUMUT3</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr"/>
+      <c r="D156" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E156" s="4" t="n">
         <v>1.0092</v>
       </c>
@@ -9421,13 +9461,13 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>REDBANK1</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
+          <t>Redbank Power Station</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr"/>
+      <c r="D157" s="3" t="n">
+        <v>150</v>
+      </c>
       <c r="E157" s="4" t="n">
         <v>0.9843</v>
       </c>
@@ -9453,13 +9493,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>HEZ</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
+          <t>Hunter Economic Zone Power Station</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="E158" s="4" t="n">
         <v>0.9969</v>
       </c>
@@ -9487,13 +9531,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>BANKSPT</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
+          <t>Bankstown Sports Club Plant Units</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E159" s="4" t="n">
         <v>1.0016</v>
       </c>
@@ -9523,13 +9571,17 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>AWABAREF</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
+          <t>Awaba Power Station</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E160" s="4" t="n">
         <v>0.9926</v>
       </c>
@@ -9561,13 +9613,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>NINEWIL</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
+          <t>Nine Network Willoughby Plant</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="E161" s="4" t="n">
         <v>1.0051</v>
       </c>
@@ -9603,13 +9659,17 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>WOYWOY</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D162" s="2" t="inlineStr"/>
+          <t>Woy Woy Landfill Site</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E162" s="4" t="n">
         <v>1.0017</v>
       </c>
@@ -9647,13 +9707,17 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>TERALBA</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D163" s="2" t="inlineStr"/>
+          <t>TERALBA POWER STATION</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="E163" s="4" t="n">
         <v>0.9926</v>
       </c>
@@ -9691,13 +9755,17 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>KINCUMB</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D164" s="2" t="inlineStr"/>
+          <t>Kincumber Landfill Site</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E164" s="4" t="n">
         <v>1.0017</v>
       </c>
@@ -9735,13 +9803,17 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>LIDDELL</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
+          <t>Liddell Power Station</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>500</v>
+      </c>
       <c r="E165" s="4" t="n">
         <v>0.9676</v>
       </c>
@@ -9779,7 +9851,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>HUNTVGT</t>
+          <t>Hunter Valley Gas Turbine</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
@@ -9823,13 +9895,17 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>AGLNOW1</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D167" s="2" t="inlineStr"/>
+          <t>West Nowra Landfill Gas Power Generation Facility</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E167" s="4" t="n">
         <v>0.9916</v>
       </c>
@@ -9867,13 +9943,17 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>AGLSITA</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D168" s="2" t="inlineStr"/>
+          <t>AGL KEMPS CREEK</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E168" s="4" t="inlineStr"/>
       <c r="F168" s="4" t="n">
         <v>1.0019</v>
@@ -9909,13 +9989,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>LIDDELL</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D169" s="2" t="inlineStr"/>
+          <t>Liddell Power Station</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>500</v>
+      </c>
       <c r="E169" s="4" t="n">
         <v>0.9676</v>
       </c>
@@ -9955,13 +10039,17 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>LIDDELL</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D170" s="2" t="inlineStr"/>
+          <t>Liddell Power Station</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>500</v>
+      </c>
       <c r="E170" s="4" t="n">
         <v>0.9676</v>
       </c>
@@ -10001,13 +10089,17 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>LIDDELL</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D171" s="2" t="inlineStr"/>
+          <t>Liddell Power Station</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>500</v>
+      </c>
       <c r="E171" s="4" t="n">
         <v>0.9676</v>
       </c>
@@ -10047,13 +10139,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>WALGBESS</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D172" s="2" t="inlineStr"/>
+          <t>Wallgrove BESS 1</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="E172" s="4" t="inlineStr"/>
       <c r="F172" s="4" t="inlineStr"/>
       <c r="G172" s="4" t="inlineStr"/>
@@ -10085,13 +10181,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>DPNTBESS</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D173" s="2" t="inlineStr"/>
+          <t>Darlington Point Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E173" s="4" t="inlineStr"/>
       <c r="F173" s="4" t="inlineStr"/>
       <c r="G173" s="4" t="inlineStr"/>
@@ -10121,13 +10221,17 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>BHBESS</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D174" s="2" t="inlineStr"/>
+          <t>Broken Hill Battery Energy Storage System</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>66</v>
+      </c>
       <c r="E174" s="4" t="inlineStr"/>
       <c r="F174" s="4" t="inlineStr"/>
       <c r="G174" s="4" t="inlineStr"/>
@@ -10155,13 +10259,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>MLLFGEF</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D175" s="2" t="inlineStr"/>
+          <t>Mugga Lane Landfill Gas To Energy Facility</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="E175" s="4" t="inlineStr"/>
       <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="4" t="inlineStr"/>
@@ -10193,13 +10301,17 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>QBYNBESS</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D176" s="2" t="inlineStr"/>
+          <t>Queanbeyan BESS</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="E176" s="4" t="inlineStr"/>
       <c r="F176" s="4" t="inlineStr"/>
       <c r="G176" s="4" t="inlineStr"/>
@@ -10229,13 +10341,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>RESS1</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D177" s="2" t="inlineStr"/>
+          <t>Riverina BESS 1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="E177" s="4" t="inlineStr"/>
       <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="4" t="inlineStr"/>
@@ -10265,13 +10381,17 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>RESS2</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D178" s="2" t="inlineStr"/>
+          <t>Riverina Energy Storage System 2</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>65</v>
+      </c>
       <c r="E178" s="4" t="inlineStr"/>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr"/>
@@ -10301,13 +10421,17 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>CBESS</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D179" s="2" t="inlineStr"/>
+          <t>Capital Battery</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>125</v>
+      </c>
       <c r="E179" s="4" t="inlineStr"/>
       <c r="F179" s="4" t="inlineStr"/>
       <c r="G179" s="4" t="inlineStr"/>
@@ -10335,13 +10459,17 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>WESTCBT</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D180" s="2" t="inlineStr"/>
+          <t>Western Suburbs League Club (Campbelltown) Plant</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E180" s="4" t="n">
         <v>0.9991</v>
       </c>
@@ -18282,11 +18410,13 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SNOWY1</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v/>
+          <t>Tumut 3 Power Station</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D36" s="4" t="n">
         <v>0.9887</v>
@@ -18309,11 +18439,13 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SNOWY1</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v/>
+          <t>Tumut 3 Power Station</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D37" s="4" t="n">
         <v>0.9887</v>
@@ -18336,11 +18468,13 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SNOWY1</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v/>
+          <t>Tumut 3 Power Station</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D38" s="4" t="n">
         <v>0.9887</v>

--- a/outputs/NSW_mlf.xlsx
+++ b/outputs/NSW_mlf.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R199"/>
+  <dimension ref="A1:R198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -676,25 +676,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WRSF1</t>
+          <t>WRWF1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>White Rock Solar Farm</t>
+          <t>White Rock Wind Farm</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="n">
+        <v>0.8468</v>
+      </c>
       <c r="H4" s="4" t="n">
         <v>0.8427</v>
       </c>
@@ -732,27 +734,25 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WRWF1</t>
+          <t>WRSF1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>White Rock Wind Farm</t>
+          <t>White Rock Solar Farm</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
-        <v>0.8468</v>
-      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="n">
         <v>0.8427</v>
       </c>
@@ -1256,12 +1256,18 @@
       <c r="L14" s="4" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="n">
+        <v>0.928</v>
+      </c>
       <c r="P14" s="4" t="n">
         <v>0.8568</v>
       </c>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="5" t="inlineStr"/>
+      <c r="Q14" s="4" t="n">
+        <v>-0.0712</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>-7.67</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2032,7 +2038,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NEWENSF1</t>
+          <t>NEWENSF2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2080,7 +2086,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NEWENSF2</t>
+          <t>NEWENSF1</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2265,13 +2271,21 @@
       <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr"/>
       <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr"/>
-      <c r="O34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="n">
+        <v>0.8284</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.9484</v>
+      </c>
       <c r="P34" s="4" t="n">
         <v>0.892</v>
       </c>
-      <c r="Q34" s="4" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr"/>
+      <c r="Q34" s="4" t="n">
+        <v>-0.0564</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>-5.95</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2515,18 +2529,26 @@
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
       <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr"/>
-      <c r="O39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.9396</v>
+      </c>
       <c r="P39" s="4" t="n">
         <v>0.9008</v>
       </c>
-      <c r="Q39" s="4" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
+      <c r="Q39" s="4" t="n">
+        <v>-0.0388</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>-4.13</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>QPSFB1</t>
+          <t>QPSFB2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2536,11 +2558,11 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr"/>
@@ -2568,7 +2590,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QPSFB2</t>
+          <t>QPSFB1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2578,11 +2600,11 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
@@ -2594,12 +2616,18 @@
       <c r="L41" s="4" t="inlineStr"/>
       <c r="M41" s="4" t="inlineStr"/>
       <c r="N41" s="4" t="inlineStr"/>
-      <c r="O41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P41" s="4" t="n">
         <v>0.9032</v>
       </c>
-      <c r="Q41" s="4" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr"/>
+      <c r="Q41" s="4" t="n">
+        <v>-0.1158</v>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>-11.36</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2629,13 +2657,21 @@
       <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr"/>
       <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.9453</v>
+      </c>
       <c r="P42" s="4" t="n">
         <v>0.9085</v>
       </c>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr"/>
+      <c r="Q42" s="4" t="n">
+        <v>-0.0368</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>-3.89</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2715,13 +2751,21 @@
       <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr"/>
-      <c r="O44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.9443</v>
+      </c>
       <c r="P44" s="4" t="n">
         <v>0.9102</v>
       </c>
-      <c r="Q44" s="4" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr"/>
+      <c r="Q44" s="4" t="n">
+        <v>-0.0341</v>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>-3.61</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2788,7 +2832,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NESBESS1</t>
+          <t>NESBESS2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2814,17 +2858,23 @@
       <c r="L46" s="4" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr"/>
-      <c r="O46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="n">
+        <v>0.8903</v>
+      </c>
       <c r="P46" s="4" t="n">
         <v>0.9197</v>
       </c>
-      <c r="Q46" s="4" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr"/>
+      <c r="Q46" s="4" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NESBESS2</t>
+          <t>NESBESS1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2850,12 +2900,18 @@
       <c r="L47" s="4" t="inlineStr"/>
       <c r="M47" s="4" t="inlineStr"/>
       <c r="N47" s="4" t="inlineStr"/>
-      <c r="O47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="n">
+        <v>0.8903</v>
+      </c>
       <c r="P47" s="4" t="n">
         <v>0.9197</v>
       </c>
-      <c r="Q47" s="4" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
+      <c r="Q47" s="4" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2922,7 +2978,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>URANQ12</t>
+          <t>URANQ11</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2984,7 +3040,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>URANQ13</t>
+          <t>URANQ12</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3046,7 +3102,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>URANQ11</t>
+          <t>URANQ13</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3216,126 +3272,126 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>WELLSF1</t>
+          <t>GUTHEGA</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wellington Solar Farm </t>
+          <t>Guthega Power Station</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.9658</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.9016</v>
+      </c>
       <c r="J54" s="4" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9125</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.9444</v>
+        <v>0.9006</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.9352</v>
+        <v>0.887</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.9439</v>
+        <v>0.893</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.9284</v>
+        <v>0.892</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.923</v>
+        <v>0.9135</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0.9273</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>0.0043</v>
+        <v>0.0138</v>
       </c>
       <c r="R54" s="5" t="n">
-        <v>0.47</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GUTHEGA</t>
+          <t>WELLSF1</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Guthega Power Station</t>
+          <t xml:space="preserve">Wellington Solar Farm </t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0.8882</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>0.9371</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>0.9658</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>0.9016</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="n">
-        <v>0.9125</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0.9006</v>
+        <v>0.9444</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.887</v>
+        <v>0.9352</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>0.893</v>
+        <v>0.9439</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.892</v>
+        <v>0.9284</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>0.9135</v>
+        <v>0.923</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0.9273</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>0.0138</v>
+        <v>0.0043</v>
       </c>
       <c r="R55" s="5" t="n">
-        <v>1.51</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NEVERSF1</t>
+          <t>NASF1</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Nevertire Solar Farm</t>
+          <t>Narromine Solar Farm</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3344,14 +3400,18 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
-      <c r="H56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0.9708</v>
+      </c>
       <c r="I56" s="4" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9603</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>0.9569</v>
@@ -3384,12 +3444,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>NASF1</t>
+          <t>NEVERSF1</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Narromine Solar Farm</t>
+          <t>Nevertire Solar Farm</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3398,18 +3458,14 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="n">
-        <v>0.9714</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>0.9708</v>
-      </c>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="n">
-        <v>0.9603</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>0.9569</v>
@@ -3712,12 +3768,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>STUBSF2</t>
+          <t>STUBSF1</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Stubbo Solar Farm 2</t>
+          <t>Stubbo Solar Farm 1</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3726,7 +3782,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr"/>
@@ -3756,12 +3812,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>STUBSF1</t>
+          <t>STUBSF2</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Stubbo Solar Farm 1</t>
+          <t>Stubbo Solar Farm 2</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3770,7 +3826,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr"/>
@@ -4168,12 +4224,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GUNNING1</t>
+          <t>CULLRGWF</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Gunning Wind Farm</t>
+          <t>Cullerin Range Wind Farm</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4182,7 +4238,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>46.5</v>
+        <v>30</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>0.9742</v>
@@ -4230,12 +4286,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>CULLRGWF</t>
+          <t>GUNNING1</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Cullerin Range Wind Farm</t>
+          <t>Gunning Wind Farm</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4244,7 +4300,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>30</v>
+        <v>46.5</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>0.9742</v>
@@ -4328,7 +4384,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HUNTER1</t>
+          <t>HUNTER2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4372,7 +4428,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HUNTER2</t>
+          <t>HUNTER1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4498,12 +4554,18 @@
       <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="4" t="inlineStr"/>
       <c r="N77" s="4" t="inlineStr"/>
-      <c r="O77" s="4" t="inlineStr"/>
+      <c r="O77" s="4" t="n">
+        <v>0.9737</v>
+      </c>
       <c r="P77" s="4" t="n">
         <v>0.955</v>
       </c>
-      <c r="Q77" s="4" t="inlineStr"/>
-      <c r="R77" s="5" t="inlineStr"/>
+      <c r="Q77" s="4" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="R77" s="5" t="n">
+        <v>-1.92</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4836,7 +4898,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>BW03</t>
+          <t>BW04</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4898,7 +4960,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BW04</t>
+          <t>BW03</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4960,7 +5022,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BW02</t>
+          <t>BW01</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5022,7 +5084,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>BW01</t>
+          <t>BW02</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5084,26 +5146,30 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GULLRWF2</t>
+          <t>GULLRSF1</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Gullen Range Wind Farm</t>
+          <t>Gullen Range Solar Farm</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr"/>
-      <c r="H88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0.9959</v>
+      </c>
       <c r="I88" s="4" t="n">
         <v>0.9694</v>
       </c>
@@ -5138,30 +5204,26 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GULLRSF1</t>
+          <t>GULLRWF2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Gullen Range Solar Farm</t>
+          <t>Gullen Range Wind Farm</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="H89" s="4" t="n">
-        <v>0.9959</v>
-      </c>
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="inlineStr"/>
       <c r="I89" s="4" t="n">
         <v>0.9694</v>
       </c>
@@ -5624,12 +5686,18 @@
       <c r="L97" s="4" t="inlineStr"/>
       <c r="M97" s="4" t="inlineStr"/>
       <c r="N97" s="4" t="inlineStr"/>
-      <c r="O97" s="4" t="inlineStr"/>
+      <c r="O97" s="4" t="n">
+        <v>0.9643</v>
+      </c>
       <c r="P97" s="4" t="n">
         <v>0.9675</v>
       </c>
-      <c r="Q97" s="4" t="inlineStr"/>
-      <c r="R97" s="5" t="inlineStr"/>
+      <c r="Q97" s="4" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="R97" s="5" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6190,21 +6258,21 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GLENNCRK</t>
+          <t>GLBWNHYD</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Glennies Creek Power Station</t>
+          <t>Glenbawn Hydro Power Station</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>12.78</v>
+        <v>5.5</v>
       </c>
       <c r="E107" s="4" t="n">
         <v>0.9828</v>
@@ -6252,21 +6320,21 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GLBWNHYD</t>
+          <t>GLENNCRK</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Glenbawn Hydro Power Station</t>
+          <t>Glennies Creek Power Station</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>5.5</v>
+        <v>12.78</v>
       </c>
       <c r="E108" s="4" t="n">
         <v>0.9828</v>
@@ -6372,7 +6440,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1-3</t>
+          <t>TUMUT1-1</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6430,7 +6498,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1-1</t>
+          <t>TUMUT1-3</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -6488,17 +6556,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1-4</t>
+          <t>TUMUT2-4</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1</t>
+          <t>TUMUT2</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="3" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>0.9768</v>
@@ -6546,7 +6614,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-1</t>
+          <t>TUMUT2-2</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6604,7 +6672,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-2</t>
+          <t>TUMUT2-1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6662,17 +6730,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-3</t>
+          <t>TUMUT1-4</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2</t>
+          <t>TUMUT1</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="3" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E115" s="4" t="n">
         <v>0.9768</v>
@@ -6720,7 +6788,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-4</t>
+          <t>TUMUT2-3</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6778,7 +6846,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>CG2</t>
+          <t>CG4</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6902,7 +6970,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>CG3</t>
+          <t>CG2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6964,7 +7032,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>CG4</t>
+          <t>CG3</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -7088,12 +7156,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>HEZ1</t>
+          <t>ERGT01</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Hunter Economic Zone</t>
+          <t>Eraring Power Station</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7102,37 +7170,49 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="4" t="inlineStr"/>
-      <c r="H122" s="4" t="inlineStr"/>
-      <c r="I122" s="4" t="inlineStr"/>
-      <c r="J122" s="4" t="inlineStr"/>
+        <v>41.5</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="J122" s="4" t="n">
+        <v>0.9835</v>
+      </c>
       <c r="K122" s="4" t="n">
-        <v>0.9897</v>
+        <v>0.9849</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.992</v>
+        <v>0.9865</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.9899</v>
+        <v>0.9848</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0.9896</v>
+        <v>0.9855</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.9931</v>
+        <v>0.9846</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>0.9831</v>
       </c>
       <c r="Q122" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.0015</v>
       </c>
       <c r="R122" s="5" t="n">
-        <v>-1.01</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="123">
@@ -7200,12 +7280,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ERGT01</t>
+          <t>HEZ1</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Eraring Power Station</t>
+          <t>Hunter Economic Zone</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7214,49 +7294,37 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>0.9856</v>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>0.9829</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="H124" s="4" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="I124" s="4" t="n">
-        <v>0.9836</v>
-      </c>
-      <c r="J124" s="4" t="n">
-        <v>0.9835</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
       <c r="K124" s="4" t="n">
-        <v>0.9849</v>
+        <v>0.9897</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.9865</v>
+        <v>0.992</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0.9848</v>
+        <v>0.9899</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>0.9855</v>
+        <v>0.9896</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.9846</v>
+        <v>0.9931</v>
       </c>
       <c r="P124" s="4" t="n">
         <v>0.9831</v>
       </c>
       <c r="Q124" s="4" t="n">
-        <v>-0.0015</v>
+        <v>-0.01</v>
       </c>
       <c r="R124" s="5" t="n">
-        <v>-0.15</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="125">
@@ -7324,7 +7392,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ER03</t>
+          <t>ER04</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -7386,7 +7454,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ER04</t>
+          <t>ER03</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -7510,7 +7578,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>VPNL1</t>
+          <t>VP5</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -7524,7 +7592,7 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>25</v>
+        <v>660</v>
       </c>
       <c r="E129" s="4" t="n">
         <v>0.9877</v>
@@ -7572,7 +7640,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>VP5</t>
+          <t>VPNL1</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -7586,7 +7654,7 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="E130" s="4" t="n">
         <v>0.9877</v>
@@ -7634,12 +7702,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>JOUNAMA1</t>
+          <t>TUMT3NL3</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Jounama Small Hydro Power Station</t>
+          <t>Tumut 3 Power Station</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7648,7 +7716,7 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E131" s="4" t="n">
         <v>0.991</v>
@@ -7696,7 +7764,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL1</t>
+          <t>TUMT3NL2</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -7758,7 +7826,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL2</t>
+          <t>TUMT3NL1</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -7820,12 +7888,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL3</t>
+          <t>JOUNAMA1</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Tumut 3 Power Station</t>
+          <t>Jounama Small Hydro Power Station</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7834,7 +7902,7 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E134" s="4" t="n">
         <v>0.991</v>
@@ -7937,13 +8005,21 @@
       <c r="K136" s="4" t="inlineStr"/>
       <c r="L136" s="4" t="inlineStr"/>
       <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr"/>
-      <c r="O136" s="4" t="inlineStr"/>
+      <c r="N136" s="4" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="O136" s="4" t="n">
+        <v>0.9901</v>
+      </c>
       <c r="P136" s="4" t="n">
         <v>0.9903</v>
       </c>
-      <c r="Q136" s="4" t="inlineStr"/>
-      <c r="R136" s="5" t="inlineStr"/>
+      <c r="Q136" s="4" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="R136" s="5" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8412,208 +8488,242 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>MLB01</t>
+          <t>THEDROP1</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Mortlake Battery Energy Storage System</t>
+          <t>The Drop Power Station</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>440</v>
-      </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
-      <c r="G145" s="4" t="inlineStr"/>
-      <c r="H145" s="4" t="inlineStr"/>
-      <c r="I145" s="4" t="inlineStr"/>
-      <c r="J145" s="4" t="inlineStr"/>
-      <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr"/>
-      <c r="N145" s="4" t="inlineStr"/>
-      <c r="O145" s="4" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>1.0157</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>1.1256</v>
+      </c>
+      <c r="H145" s="4" t="n">
+        <v>1.1441</v>
+      </c>
+      <c r="I145" s="4" t="n">
+        <v>0.9895</v>
+      </c>
+      <c r="J145" s="4" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="K145" s="4" t="n">
+        <v>0.9686</v>
+      </c>
+      <c r="L145" s="4" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="M145" s="4" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="N145" s="4" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="O145" s="4" t="n">
+        <v>0.9712</v>
+      </c>
       <c r="P145" s="4" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="Q145" s="4" t="inlineStr"/>
-      <c r="R145" s="5" t="inlineStr"/>
+        <v>0.9944</v>
+      </c>
+      <c r="Q145" s="4" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="R145" s="5" t="n">
+        <v>2.39</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>THEDROP1</t>
+          <t>APPIN</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>The Drop Power Station</t>
+          <t>Appin Power Plant</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>2.5</v>
+        <v>55.6</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>0.967</v>
+        <v>0.9998</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>1.0157</v>
+        <v>0.9986</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>1.1256</v>
+        <v>1</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>1.1441</v>
+        <v>1.001</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.9895</v>
+        <v>0.9953</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>0.9537</v>
+        <v>0.9978</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0.9686</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="L146" s="4" t="n">
-        <v>0.9708</v>
+        <v>0.9973</v>
       </c>
       <c r="M146" s="4" t="n">
-        <v>0.9687</v>
+        <v>0.995</v>
       </c>
       <c r="N146" s="4" t="n">
-        <v>0.9563</v>
+        <v>0.9929</v>
       </c>
       <c r="O146" s="4" t="n">
-        <v>0.9712</v>
+        <v>0.995</v>
       </c>
       <c r="P146" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9948</v>
       </c>
       <c r="Q146" s="4" t="n">
-        <v>0.0232</v>
+        <v>-0.0002</v>
       </c>
       <c r="R146" s="5" t="n">
-        <v>2.39</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>APPIN</t>
+          <t>WTAHB1</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Appin Power Plant</t>
+          <t>Waratah Super Battery</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="E147" s="4" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="F147" s="4" t="n">
-        <v>0.9986</v>
-      </c>
-      <c r="G147" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="I147" s="4" t="n">
-        <v>0.9953</v>
-      </c>
-      <c r="J147" s="4" t="n">
-        <v>0.9978</v>
-      </c>
-      <c r="K147" s="4" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="L147" s="4" t="n">
-        <v>0.9973</v>
-      </c>
-      <c r="M147" s="4" t="n">
-        <v>0.995</v>
-      </c>
+        <v>1095.84</v>
+      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr"/>
+      <c r="M147" s="4" t="inlineStr"/>
       <c r="N147" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.997</v>
       </c>
       <c r="O147" s="4" t="n">
-        <v>0.995</v>
+        <v>0.9923</v>
       </c>
       <c r="P147" s="4" t="n">
-        <v>0.9948</v>
+        <v>0.9972</v>
       </c>
       <c r="Q147" s="4" t="n">
-        <v>-0.0002</v>
+        <v>0.0049</v>
       </c>
       <c r="R147" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>WTAHB1</t>
+          <t>WYANGALB</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Waratah Super Battery</t>
+          <t>Wyangala B Power Station</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>1095.84</v>
-      </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
-      <c r="G148" s="4" t="inlineStr"/>
-      <c r="H148" s="4" t="inlineStr"/>
-      <c r="I148" s="4" t="inlineStr"/>
-      <c r="J148" s="4" t="inlineStr"/>
-      <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr"/>
-      <c r="M148" s="4" t="inlineStr"/>
-      <c r="N148" s="4" t="inlineStr"/>
-      <c r="O148" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>1.0099</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>1.0355</v>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>1.0435</v>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>1.0411</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>1.0314</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="K148" s="4" t="n">
+        <v>0.9721</v>
+      </c>
+      <c r="L148" s="4" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="M148" s="4" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="N148" s="4" t="n">
+        <v>0.9971</v>
+      </c>
+      <c r="O148" s="4" t="n">
+        <v>0.9858</v>
+      </c>
       <c r="P148" s="4" t="n">
-        <v>0.9972</v>
-      </c>
-      <c r="Q148" s="4" t="inlineStr"/>
-      <c r="R148" s="5" t="inlineStr"/>
+        <v>0.998</v>
+      </c>
+      <c r="Q148" s="4" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="R148" s="5" t="n">
+        <v>1.24</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>WYANGALB</t>
+          <t>WYANGALA</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Wyangala B Power Station</t>
+          <t>Wyangala A Power Station</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -8622,7 +8732,7 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E149" s="4" t="n">
         <v>1.0099</v>
@@ -8670,100 +8780,108 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>WYANGALA</t>
+          <t>QBYNB1</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Wyangala A Power Station</t>
+          <t>Queanbeyan BESS</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E150" s="4" t="n">
-        <v>1.0099</v>
-      </c>
-      <c r="F150" s="4" t="n">
-        <v>1.0355</v>
-      </c>
-      <c r="G150" s="4" t="n">
-        <v>1.0435</v>
-      </c>
-      <c r="H150" s="4" t="n">
-        <v>1.0411</v>
-      </c>
-      <c r="I150" s="4" t="n">
-        <v>1.0314</v>
-      </c>
-      <c r="J150" s="4" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="K150" s="4" t="n">
-        <v>0.9721</v>
-      </c>
-      <c r="L150" s="4" t="n">
-        <v>0.9746</v>
-      </c>
-      <c r="M150" s="4" t="n">
-        <v>0.9378</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr"/>
+      <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr"/>
+      <c r="K150" s="4" t="inlineStr"/>
+      <c r="L150" s="4" t="inlineStr"/>
+      <c r="M150" s="4" t="inlineStr"/>
       <c r="N150" s="4" t="n">
-        <v>0.9971</v>
+        <v>0.9795</v>
       </c>
       <c r="O150" s="4" t="n">
-        <v>0.9858</v>
+        <v>1.0072</v>
       </c>
       <c r="P150" s="4" t="n">
-        <v>0.998</v>
+        <v>0.9982</v>
       </c>
       <c r="Q150" s="4" t="n">
-        <v>0.0122</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="R150" s="5" t="n">
-        <v>1.24</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>QBYNB1</t>
+          <t>LUCAS2S2</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Queanbeyan BESS</t>
+          <t>Lucas Heights 2 Power Station</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
-      <c r="G151" s="4" t="inlineStr"/>
-      <c r="H151" s="4" t="inlineStr"/>
-      <c r="I151" s="4" t="inlineStr"/>
-      <c r="J151" s="4" t="inlineStr"/>
-      <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="4" t="inlineStr"/>
-      <c r="M151" s="4" t="inlineStr"/>
-      <c r="N151" s="4" t="inlineStr"/>
-      <c r="O151" s="4" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>1.0029</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="K151" s="4" t="n">
+        <v>1.0015</v>
+      </c>
+      <c r="L151" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="M151" s="4" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="N151" s="4" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="O151" s="4" t="n">
+        <v>0.9987</v>
+      </c>
       <c r="P151" s="4" t="n">
-        <v>0.9982</v>
-      </c>
-      <c r="Q151" s="4" t="inlineStr"/>
-      <c r="R151" s="5" t="inlineStr"/>
+        <v>0.9983</v>
+      </c>
+      <c r="Q151" s="4" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="R151" s="5" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8830,12 +8948,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>LUCAS2S2</t>
+          <t>GRANGEAV</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Lucas Heights 2 Power Station</t>
+          <t>Grange Avenue Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -8844,122 +8962,122 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1.0016</v>
+        <v>0.9996</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1.0029</v>
+        <v>0.9991</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1.0033</v>
+        <v>0.9989</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1.0036</v>
+        <v>0.9991</v>
       </c>
       <c r="I153" s="4" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" s="4" t="n">
         <v>1.0001</v>
       </c>
-      <c r="J153" s="4" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="K153" s="4" t="n">
-        <v>1.0015</v>
-      </c>
-      <c r="L153" s="4" t="n">
-        <v>1.0009</v>
-      </c>
       <c r="M153" s="4" t="n">
-        <v>0.9988</v>
+        <v>0.9998</v>
       </c>
       <c r="N153" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9998</v>
       </c>
       <c r="O153" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="P153" s="4" t="n">
-        <v>0.9983</v>
+        <v>0.9993</v>
       </c>
       <c r="Q153" s="4" t="n">
-        <v>-0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="R153" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GRANGEAV</t>
+          <t>TOWER</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Grange Avenue Landfill Gas Power Station</t>
+          <t>Tower Power Plant</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>2</v>
+        <v>41.2</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>0.9996</v>
+        <v>1.002</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>0.9991</v>
+        <v>1.0019</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>0.9989</v>
+        <v>1.0022</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>0.9991</v>
+        <v>1.0024</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>0.9997</v>
+        <v>1.0009</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>0.9997</v>
+        <v>1.0012</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>1.0015</v>
       </c>
       <c r="L154" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.0011</v>
       </c>
       <c r="M154" s="4" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="N154" s="4" t="n">
         <v>0.9998</v>
       </c>
       <c r="O154" s="4" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="P154" s="4" t="n">
-        <v>0.9993</v>
+        <v>0.9998</v>
       </c>
       <c r="Q154" s="4" t="n">
-        <v>-0.0002</v>
+        <v>-0.0012</v>
       </c>
       <c r="R154" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TOWER</t>
+          <t>TAHMOOR1</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Tower Power Plant</t>
+          <t>Tahmoor Waste Coal Mine Gas Power Station</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -8968,10 +9086,10 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>41.2</v>
+        <v>7.042</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="F155" s="4" t="n">
         <v>1.0019</v>
@@ -9016,132 +9134,132 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TAHMOOR1</t>
+          <t>DG_NSW1</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Tahmoor Waste Coal Mine Gas Power Station</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>NSW1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr"/>
       <c r="D156" s="3" t="n">
-        <v>7.042</v>
+        <v>3000</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1.0019</v>
+        <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1.0022</v>
+        <v>1</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>1.0024</v>
+        <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.0009</v>
+        <v>1</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>1.0012</v>
+        <v>1</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1.0015</v>
+        <v>1</v>
       </c>
       <c r="L156" s="4" t="n">
-        <v>1.0011</v>
+        <v>1</v>
       </c>
       <c r="M156" s="4" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="N156" s="4" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="O156" s="4" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="P156" s="4" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="4" t="n">
-        <v>-0.0012</v>
+        <v>0</v>
       </c>
       <c r="R156" s="5" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>DG_NSW1</t>
+          <t>STGEORG1</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>NSW1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr"/>
+          <t>St George Leagues Plant</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D157" s="3" t="n">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1</v>
+        <v>1.0059</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>1</v>
+        <v>1.0071</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>1</v>
+        <v>1.0069</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>1</v>
+        <v>1.0063</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>1</v>
+        <v>1.003</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>1</v>
+        <v>1.0035</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>1.0045</v>
       </c>
       <c r="L157" s="4" t="n">
-        <v>1</v>
+        <v>1.0037</v>
       </c>
       <c r="M157" s="4" t="n">
-        <v>1</v>
+        <v>1.0013</v>
       </c>
       <c r="N157" s="4" t="n">
-        <v>1</v>
+        <v>1.0009</v>
       </c>
       <c r="O157" s="4" t="n">
-        <v>1</v>
+        <v>1.0013</v>
       </c>
       <c r="P157" s="4" t="n">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
       <c r="Q157" s="4" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="R157" s="5" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>STGEORG1</t>
+          <t>SITHE01</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>St George Leagues Plant</t>
+          <t>Smithfield Energy Facility</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -9150,111 +9268,111 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>1.0018</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>1.0035</v>
+      </c>
+      <c r="G158" s="4" t="n">
+        <v>1.0041</v>
+      </c>
+      <c r="H158" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E158" s="4" t="n">
-        <v>1.0059</v>
-      </c>
-      <c r="F158" s="4" t="n">
-        <v>1.0071</v>
-      </c>
-      <c r="G158" s="4" t="n">
-        <v>1.0069</v>
-      </c>
-      <c r="H158" s="4" t="n">
-        <v>1.0063</v>
-      </c>
       <c r="I158" s="4" t="n">
-        <v>1.003</v>
+        <v>1.0029</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1.0035</v>
+        <v>1.0025</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1.0045</v>
+        <v>1.0017</v>
       </c>
       <c r="L158" s="4" t="n">
-        <v>1.0037</v>
+        <v>1.0018</v>
       </c>
       <c r="M158" s="4" t="n">
-        <v>1.0013</v>
+        <v>1.0015</v>
       </c>
       <c r="N158" s="4" t="n">
-        <v>1.0009</v>
+        <v>1.0015</v>
       </c>
       <c r="O158" s="4" t="n">
-        <v>1.0013</v>
+        <v>1.0017</v>
       </c>
       <c r="P158" s="4" t="n">
-        <v>1.0008</v>
+        <v>1.0015</v>
       </c>
       <c r="Q158" s="4" t="n">
-        <v>-0.0005</v>
+        <v>-0.0002</v>
       </c>
       <c r="R158" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SITHE01</t>
+          <t>EASTCRK2</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Smithfield Energy Facility</t>
+          <t>Eastern Creek 2 Gas Utilisation Facility</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>125</v>
+        <v>6.738</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1.0018</v>
+        <v>1.0021</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1.0035</v>
+        <v>1.0021</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>1.0041</v>
+        <v>1.0021</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>1</v>
+        <v>1.0021</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.0021</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>1.0025</v>
+        <v>1.001</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1.0017</v>
+        <v>1.001</v>
       </c>
       <c r="L159" s="4" t="n">
-        <v>1.0018</v>
+        <v>1.001</v>
       </c>
       <c r="M159" s="4" t="n">
-        <v>1.0015</v>
+        <v>1.001</v>
       </c>
       <c r="N159" s="4" t="n">
-        <v>1.0015</v>
+        <v>1.001</v>
       </c>
       <c r="O159" s="4" t="n">
-        <v>1.0017</v>
+        <v>1.0016</v>
       </c>
       <c r="P159" s="4" t="n">
-        <v>1.0015</v>
+        <v>1.0016</v>
       </c>
       <c r="Q159" s="4" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="R159" s="5" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -9322,74 +9440,56 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>EASTCRK2</t>
+          <t>WALGRV1</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Eastern Creek 2 Gas Utilisation Facility</t>
+          <t>Wallgrove BESS 1</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>6.738</v>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="F161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="G161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="H161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="I161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="J161" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="K161" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="M161" s="4" t="n">
-        <v>1.001</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr"/>
+      <c r="G161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr"/>
       <c r="N161" s="4" t="n">
-        <v>1.001</v>
+        <v>1.0009</v>
       </c>
       <c r="O161" s="4" t="n">
-        <v>1.0016</v>
+        <v>1.0015</v>
       </c>
       <c r="P161" s="4" t="n">
-        <v>1.0016</v>
+        <v>1.0017</v>
       </c>
       <c r="Q161" s="4" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="R161" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>WALGRV1</t>
+          <t>SMTHBES1</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Wallgrove BESS 1</t>
+          <t>Smithfield Battery Energy Storage System, Units 1 - 36</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -9398,7 +9498,7 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>50</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E162" s="4" t="inlineStr"/>
       <c r="F162" s="4" t="inlineStr"/>
@@ -9410,109 +9510,141 @@
       <c r="L162" s="4" t="inlineStr"/>
       <c r="M162" s="4" t="inlineStr"/>
       <c r="N162" s="4" t="inlineStr"/>
-      <c r="O162" s="4" t="inlineStr"/>
+      <c r="O162" s="4" t="n">
+        <v>1.0017</v>
+      </c>
       <c r="P162" s="4" t="n">
-        <v>1.0017</v>
-      </c>
-      <c r="Q162" s="4" t="inlineStr"/>
-      <c r="R162" s="5" t="inlineStr"/>
+        <v>1.0019</v>
+      </c>
+      <c r="Q162" s="4" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="R162" s="5" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SMTHBES1</t>
+          <t>CESF1</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Smithfield Battery Energy Storage System, Units 1 - 36</t>
+          <t>Capital East Solar Farm</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="E163" s="4" t="inlineStr"/>
-      <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr"/>
-      <c r="H163" s="4" t="inlineStr"/>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
-      <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr"/>
-      <c r="M163" s="4" t="inlineStr"/>
-      <c r="N163" s="4" t="inlineStr"/>
-      <c r="O163" s="4" t="inlineStr"/>
+        <v>0.205</v>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>1.0257</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>1.0563</v>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>1.0438</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="J163" s="4" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="K163" s="4" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="L163" s="4" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="M163" s="4" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="N163" s="4" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="O163" s="4" t="n">
+        <v>0.9954</v>
+      </c>
       <c r="P163" s="4" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="Q163" s="4" t="inlineStr"/>
-      <c r="R163" s="5" t="inlineStr"/>
+        <v>1.0026</v>
+      </c>
+      <c r="Q163" s="4" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="R163" s="5" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>CESF1</t>
+          <t>TARALGA1</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Capital East Solar Farm</t>
+          <t>Taralga Wind Farm</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>0.205</v>
+        <v>106.8</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>1.0257</v>
+        <v>0.9922</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>1.0563</v>
+        <v>0.9998</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>1.0438</v>
+        <v>0.9977</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>0.989</v>
+        <v>1.0086</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>0.9982</v>
+        <v>1.0103</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0.9882</v>
+        <v>1.0122</v>
       </c>
       <c r="L164" s="4" t="n">
-        <v>0.9866</v>
+        <v>1.0118</v>
       </c>
       <c r="M164" s="4" t="n">
-        <v>0.9867</v>
+        <v>1.0095</v>
       </c>
       <c r="N164" s="4" t="n">
-        <v>0.9751</v>
+        <v>1.0088</v>
       </c>
       <c r="O164" s="4" t="n">
-        <v>0.9954</v>
+        <v>0.9971</v>
       </c>
       <c r="P164" s="4" t="n">
-        <v>1.0026</v>
+        <v>1.0029</v>
       </c>
       <c r="Q164" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.0058</v>
       </c>
       <c r="R164" s="5" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="165">
@@ -9580,12 +9712,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TARALGA1</t>
+          <t>FLYCRKWF</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Taralga Wind Farm</t>
+          <t>Flyers Creek Wind Farm</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -9594,163 +9726,159 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>106.8</v>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>0.9844000000000001</v>
-      </c>
-      <c r="F166" s="4" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="H166" s="4" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="I166" s="4" t="n">
-        <v>1.0086</v>
-      </c>
-      <c r="J166" s="4" t="n">
-        <v>1.0103</v>
-      </c>
-      <c r="K166" s="4" t="n">
-        <v>1.0122</v>
-      </c>
-      <c r="L166" s="4" t="n">
-        <v>1.0118</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="E166" s="4" t="inlineStr"/>
+      <c r="F166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr"/>
+      <c r="K166" s="4" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
       <c r="M166" s="4" t="n">
-        <v>1.0095</v>
+        <v>1.0266</v>
       </c>
       <c r="N166" s="4" t="n">
-        <v>1.0088</v>
+        <v>1.0205</v>
       </c>
       <c r="O166" s="4" t="n">
-        <v>0.9971</v>
+        <v>1.0278</v>
       </c>
       <c r="P166" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.0047</v>
       </c>
       <c r="Q166" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0231</v>
       </c>
       <c r="R166" s="5" t="n">
-        <v>0.58</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>FLYCRKWF</t>
+          <t>GUTHNL1</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Flyers Creek Wind Farm</t>
+          <t>Guthega Power Station</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="E167" s="4" t="inlineStr"/>
-      <c r="F167" s="4" t="inlineStr"/>
-      <c r="G167" s="4" t="inlineStr"/>
-      <c r="H167" s="4" t="inlineStr"/>
-      <c r="I167" s="4" t="inlineStr"/>
-      <c r="J167" s="4" t="inlineStr"/>
-      <c r="K167" s="4" t="inlineStr"/>
-      <c r="L167" s="4" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>1.0148</v>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>1.0426</v>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v>1.0256</v>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="J167" s="4" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="K167" s="4" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="L167" s="4" t="n">
+        <v>0.9633</v>
+      </c>
       <c r="M167" s="4" t="n">
-        <v>1.0266</v>
+        <v>0.9838</v>
       </c>
       <c r="N167" s="4" t="n">
-        <v>1.0205</v>
+        <v>0.9795</v>
       </c>
       <c r="O167" s="4" t="n">
-        <v>1.0278</v>
+        <v>1.0003</v>
       </c>
       <c r="P167" s="4" t="n">
-        <v>1.0047</v>
+        <v>1.0048</v>
       </c>
       <c r="Q167" s="4" t="n">
-        <v>-0.0231</v>
+        <v>0.0045</v>
       </c>
       <c r="R167" s="5" t="n">
-        <v>-2.25</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GUTHNL1</t>
+          <t>TUMUT3-5</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Guthega Power Station</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Hydro</t>
-        </is>
-      </c>
+          <t>TUMUT3</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr"/>
       <c r="D168" s="3" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>0.9549</v>
+        <v>1.0092</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>1.0148</v>
+        <v>1.0092</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>1.0426</v>
+        <v>1.0092</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>1.0256</v>
+        <v>1.0092</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>0.9922</v>
+        <v>1.0092</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>0.9865</v>
+        <v>1.0092</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0.9762</v>
+        <v>1.0092</v>
       </c>
       <c r="L168" s="4" t="n">
-        <v>0.9633</v>
+        <v>1.0092</v>
       </c>
       <c r="M168" s="4" t="n">
-        <v>0.9838</v>
+        <v>1.0092</v>
       </c>
       <c r="N168" s="4" t="n">
-        <v>0.9795</v>
+        <v>1.0092</v>
       </c>
       <c r="O168" s="4" t="n">
-        <v>1.0003</v>
+        <v>1.0092</v>
       </c>
       <c r="P168" s="4" t="n">
-        <v>1.0048</v>
+        <v>1.0092</v>
       </c>
       <c r="Q168" s="4" t="n">
-        <v>0.0045</v>
+        <v>0</v>
       </c>
       <c r="R168" s="5" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-1</t>
+          <t>TUMUT3-4</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -9808,7 +9936,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-3</t>
+          <t>TUMUT3-6</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -9866,7 +9994,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-4</t>
+          <t>TUMUT3-2</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -9924,7 +10052,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-5</t>
+          <t>TUMUT3-1</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -9982,7 +10110,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-6</t>
+          <t>TUMUT3-3</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -10040,81 +10168,65 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-2</t>
+          <t>CAPBES1</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr"/>
+          <t>Capital Battery</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
       <c r="D174" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="F174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="G174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="H174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="I174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="J174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="K174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="L174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="M174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E174" s="4" t="inlineStr"/>
+      <c r="F174" s="4" t="inlineStr"/>
+      <c r="G174" s="4" t="inlineStr"/>
+      <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr"/>
+      <c r="J174" s="4" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr"/>
+      <c r="L174" s="4" t="inlineStr"/>
+      <c r="M174" s="4" t="inlineStr"/>
       <c r="N174" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0084</v>
       </c>
       <c r="O174" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0389</v>
       </c>
       <c r="P174" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0263</v>
       </c>
       <c r="Q174" s="4" t="n">
-        <v>0</v>
+        <v>-0.0126</v>
       </c>
       <c r="R174" s="5" t="n">
-        <v>0</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>CAPBES1</t>
+          <t>REDBANK1</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Capital Battery</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
+          <t>Redbank Power Station</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr"/>
       <c r="D175" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="E175" s="4" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="E175" s="4" t="n">
+        <v>0.9843</v>
+      </c>
       <c r="F175" s="4" t="inlineStr"/>
       <c r="G175" s="4" t="inlineStr"/>
       <c r="H175" s="4" t="inlineStr"/>
@@ -10125,31 +10237,35 @@
       <c r="M175" s="4" t="inlineStr"/>
       <c r="N175" s="4" t="inlineStr"/>
       <c r="O175" s="4" t="inlineStr"/>
-      <c r="P175" s="4" t="n">
-        <v>1.0263</v>
-      </c>
+      <c r="P175" s="4" t="inlineStr"/>
       <c r="Q175" s="4" t="inlineStr"/>
       <c r="R175" s="5" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>REDBANK1</t>
+          <t>HEZ</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Redbank Power Station</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr"/>
+          <t>Hunter Economic Zone Power Station</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D176" s="3" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>0.9843</v>
-      </c>
-      <c r="F176" s="4" t="inlineStr"/>
+        <v>0.9969</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>0.9967</v>
+      </c>
       <c r="G176" s="4" t="inlineStr"/>
       <c r="H176" s="4" t="inlineStr"/>
       <c r="I176" s="4" t="inlineStr"/>
@@ -10166,12 +10282,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>HEZ</t>
+          <t>BANKSPT1</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Hunter Economic Zone Power Station</t>
+          <t>Bankstown Sports Club Plant Units</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -10180,15 +10296,17 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>0.9969</v>
+        <v>1.0016</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>0.9967</v>
-      </c>
-      <c r="G177" s="4" t="inlineStr"/>
+        <v>1.0029</v>
+      </c>
+      <c r="G177" s="4" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="H177" s="4" t="inlineStr"/>
       <c r="I177" s="4" t="inlineStr"/>
       <c r="J177" s="4" t="inlineStr"/>
@@ -10204,32 +10322,34 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>BANKSPT1</t>
+          <t>AWABAREF</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Bankstown Sports Club Plant Units</t>
+          <t>Awaba Power Station</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>1.0016</v>
+        <v>0.9926</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>1.0029</v>
+        <v>0.9907</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
+        <v>0.9892</v>
+      </c>
+      <c r="H178" s="4" t="n">
+        <v>0.9901</v>
+      </c>
       <c r="I178" s="4" t="inlineStr"/>
       <c r="J178" s="4" t="inlineStr"/>
       <c r="K178" s="4" t="inlineStr"/>
@@ -10244,36 +10364,40 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AWABAREF</t>
+          <t>NINEWIL1</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Awaba Power Station</t>
+          <t>Nine Network Willoughby Plant</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>0.9926</v>
+        <v>1.0051</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>0.9907</v>
+        <v>1.005</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>0.9892</v>
+        <v>1.0048</v>
       </c>
       <c r="H179" s="4" t="n">
-        <v>0.9901</v>
-      </c>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr"/>
+        <v>1.0049</v>
+      </c>
+      <c r="I179" s="4" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v>1.0058</v>
+      </c>
       <c r="K179" s="4" t="inlineStr"/>
       <c r="L179" s="4" t="inlineStr"/>
       <c r="M179" s="4" t="inlineStr"/>
@@ -10286,41 +10410,43 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>NINEWIL1</t>
+          <t>TERALBA</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Nine Network Willoughby Plant</t>
+          <t>TERALBA POWER STATION</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1.0051</v>
+        <v>0.9926</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>1.005</v>
+        <v>0.9907</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>1.0048</v>
+        <v>0.9892</v>
       </c>
       <c r="H180" s="4" t="n">
-        <v>1.0049</v>
+        <v>0.9901</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>1.007</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>1.0058</v>
-      </c>
-      <c r="K180" s="4" t="inlineStr"/>
+        <v>0.9907</v>
+      </c>
+      <c r="K180" s="4" t="n">
+        <v>0.9917</v>
+      </c>
       <c r="L180" s="4" t="inlineStr"/>
       <c r="M180" s="4" t="inlineStr"/>
       <c r="N180" s="4" t="inlineStr"/>
@@ -10380,42 +10506,38 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TERALBA</t>
+          <t>HVGTS</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>TERALBA POWER STATION</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="n">
-        <v>3</v>
-      </c>
+          <t>Hunter Valley Gas Turbine</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
       <c r="E182" s="4" t="n">
-        <v>0.9926</v>
+        <v>0.974</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>0.9907</v>
+        <v>0.9679</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>0.9892</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="H182" s="4" t="n">
-        <v>0.9901</v>
+        <v>0.9596</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9654</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>0.9907</v>
+        <v>0.9673</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0.9917</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="L182" s="4" t="inlineStr"/>
       <c r="M182" s="4" t="inlineStr"/>
@@ -10428,12 +10550,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>KINCUM1</t>
+          <t>AGLSITA1</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Kincumber Landfill Site</t>
+          <t>AGL KEMPS CREEK</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -10444,26 +10566,24 @@
       <c r="D183" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="4" t="n">
-        <v>1.0017</v>
-      </c>
+      <c r="E183" s="4" t="inlineStr"/>
       <c r="F183" s="4" t="n">
+        <v>1.0019</v>
+      </c>
+      <c r="G183" s="4" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="H183" s="4" t="n">
+        <v>1.0024</v>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="J183" s="4" t="n">
+        <v>1.0012</v>
+      </c>
+      <c r="K183" s="4" t="n">
         <v>1.0015</v>
-      </c>
-      <c r="G183" s="4" t="n">
-        <v>1.0008</v>
-      </c>
-      <c r="H183" s="4" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="I183" s="4" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J183" s="4" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="K183" s="4" t="n">
-        <v>1.0037</v>
       </c>
       <c r="L183" s="4" t="inlineStr"/>
       <c r="M183" s="4" t="inlineStr"/>
@@ -10476,42 +10596,42 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>LD03</t>
+          <t>AGLNOW1</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Liddell Power Station</t>
+          <t>West Nowra Landfill Gas Power Generation Facility</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>0.9676</v>
+        <v>0.9916</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>0.9593</v>
+        <v>0.9986</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>0.9509</v>
+        <v>1.0023</v>
       </c>
       <c r="H184" s="4" t="n">
-        <v>0.9537</v>
+        <v>1.0037</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0.9593</v>
+        <v>0.9929</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>0.9631</v>
+        <v>0.9967</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0.9628</v>
+        <v>0.9929</v>
       </c>
       <c r="L184" s="4" t="inlineStr"/>
       <c r="M184" s="4" t="inlineStr"/>
@@ -10524,38 +10644,42 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>HVGTS</t>
+          <t>KINCUM1</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Hunter Valley Gas Turbine</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D185" s="2" t="inlineStr"/>
+          <t>Kincumber Landfill Site</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E185" s="4" t="n">
-        <v>0.974</v>
+        <v>1.0017</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>0.9679</v>
+        <v>1.0015</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>0.9582000000000001</v>
+        <v>1.0008</v>
       </c>
       <c r="H185" s="4" t="n">
-        <v>0.9596</v>
+        <v>1.0011</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>0.9654</v>
+        <v>1.0036</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>0.9673</v>
+        <v>1.0019</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0.9651999999999999</v>
+        <v>1.0037</v>
       </c>
       <c r="L185" s="4" t="inlineStr"/>
       <c r="M185" s="4" t="inlineStr"/>
@@ -10568,42 +10692,42 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>AGLNOW1</t>
+          <t>LD03</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>West Nowra Landfill Gas Power Generation Facility</t>
+          <t>Liddell Power Station</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>0.9916</v>
+        <v>0.9676</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9593</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>1.0023</v>
+        <v>0.9509</v>
       </c>
       <c r="H186" s="4" t="n">
-        <v>1.0037</v>
+        <v>0.9537</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.9593</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>0.9967</v>
+        <v>0.9631</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.9628</v>
       </c>
       <c r="L186" s="4" t="inlineStr"/>
       <c r="M186" s="4" t="inlineStr"/>
@@ -10616,42 +10740,46 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>AGLSITA1</t>
+          <t>LD04</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>AGL KEMPS CREEK</t>
+          <t>Liddell Power Station</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" s="4" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="E187" s="4" t="n">
+        <v>0.9676</v>
+      </c>
       <c r="F187" s="4" t="n">
-        <v>1.0019</v>
+        <v>0.9593</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>1.0022</v>
+        <v>0.9509</v>
       </c>
       <c r="H187" s="4" t="n">
-        <v>1.0024</v>
+        <v>0.9537</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>1.0009</v>
+        <v>0.9593</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>1.0012</v>
+        <v>0.9631</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>1.0015</v>
-      </c>
-      <c r="L187" s="4" t="inlineStr"/>
+        <v>0.9628</v>
+      </c>
+      <c r="L187" s="4" t="n">
+        <v>0.9659</v>
+      </c>
       <c r="M187" s="4" t="inlineStr"/>
       <c r="N187" s="4" t="inlineStr"/>
       <c r="O187" s="4" t="inlineStr"/>
@@ -10662,7 +10790,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>LD01</t>
+          <t>LD02</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -10712,7 +10840,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>LD02</t>
+          <t>LD01</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -10762,48 +10890,40 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>LD04</t>
+          <t>WALGRVG1</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Liddell Power Station</t>
+          <t>Wallgrove BESS 1</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="E190" s="4" t="n">
-        <v>0.9676</v>
-      </c>
-      <c r="F190" s="4" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="G190" s="4" t="n">
-        <v>0.9509</v>
-      </c>
-      <c r="H190" s="4" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="I190" s="4" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="J190" s="4" t="n">
-        <v>0.9631</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E190" s="4" t="inlineStr"/>
+      <c r="F190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="inlineStr"/>
+      <c r="H190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr"/>
+      <c r="J190" s="4" t="inlineStr"/>
       <c r="K190" s="4" t="n">
-        <v>0.9628</v>
+        <v>1.0011</v>
       </c>
       <c r="L190" s="4" t="n">
-        <v>0.9659</v>
-      </c>
-      <c r="M190" s="4" t="inlineStr"/>
-      <c r="N190" s="4" t="inlineStr"/>
+        <v>1.001</v>
+      </c>
+      <c r="M190" s="4" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="N190" s="4" t="n">
+        <v>1.001</v>
+      </c>
       <c r="O190" s="4" t="inlineStr"/>
       <c r="P190" s="4" t="inlineStr"/>
       <c r="Q190" s="4" t="inlineStr"/>
@@ -10812,21 +10932,21 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>WALGRVG1</t>
+          <t>MLLFGEF1</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Wallgrove BESS 1</t>
+          <t>Mugga Lane Landfill Gas To Energy Facility</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E191" s="4" t="inlineStr"/>
       <c r="F191" s="4" t="inlineStr"/>
@@ -10835,16 +10955,16 @@
       <c r="I191" s="4" t="inlineStr"/>
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="n">
-        <v>1.0011</v>
+        <v>0.9683</v>
       </c>
       <c r="L191" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9687</v>
       </c>
       <c r="M191" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9663</v>
       </c>
       <c r="N191" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9567</v>
       </c>
       <c r="O191" s="4" t="inlineStr"/>
       <c r="P191" s="4" t="inlineStr"/>
@@ -10854,12 +10974,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>DPNTBG1</t>
+          <t>BHBG1</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Darlington Point Energy Storage System</t>
+          <t>Broken Hill Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -10868,7 +10988,7 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E192" s="4" t="inlineStr"/>
       <c r="F192" s="4" t="inlineStr"/>
@@ -10877,14 +10997,12 @@
       <c r="I192" s="4" t="inlineStr"/>
       <c r="J192" s="4" t="inlineStr"/>
       <c r="K192" s="4" t="inlineStr"/>
-      <c r="L192" s="4" t="n">
-        <v>0.9402</v>
-      </c>
+      <c r="L192" s="4" t="inlineStr"/>
       <c r="M192" s="4" t="n">
-        <v>0.9089</v>
+        <v>0.8671</v>
       </c>
       <c r="N192" s="4" t="n">
-        <v>0.9048</v>
+        <v>0.8423</v>
       </c>
       <c r="O192" s="4" t="inlineStr"/>
       <c r="P192" s="4" t="inlineStr"/>
@@ -10894,12 +11012,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>BHBG1</t>
+          <t>CAPBES1G</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Broken Hill Battery Energy Storage System</t>
+          <t>Capital Battery</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -10908,7 +11026,7 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="E193" s="4" t="inlineStr"/>
       <c r="F193" s="4" t="inlineStr"/>
@@ -10919,10 +11037,10 @@
       <c r="K193" s="4" t="inlineStr"/>
       <c r="L193" s="4" t="inlineStr"/>
       <c r="M193" s="4" t="n">
-        <v>0.8671</v>
+        <v>0.9704</v>
       </c>
       <c r="N193" s="4" t="n">
-        <v>0.8423</v>
+        <v>0.9337</v>
       </c>
       <c r="O193" s="4" t="inlineStr"/>
       <c r="P193" s="4" t="inlineStr"/>
@@ -10932,21 +11050,21 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>MLLFGEF1</t>
+          <t>QBYNBG1</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Mugga Lane Landfill Gas To Energy Facility</t>
+          <t>Queanbeyan BESS</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E194" s="4" t="inlineStr"/>
       <c r="F194" s="4" t="inlineStr"/>
@@ -10954,17 +11072,15 @@
       <c r="H194" s="4" t="inlineStr"/>
       <c r="I194" s="4" t="inlineStr"/>
       <c r="J194" s="4" t="inlineStr"/>
-      <c r="K194" s="4" t="n">
-        <v>0.9683</v>
-      </c>
+      <c r="K194" s="4" t="inlineStr"/>
       <c r="L194" s="4" t="n">
-        <v>0.9687</v>
+        <v>0.9752</v>
       </c>
       <c r="M194" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.979</v>
       </c>
       <c r="N194" s="4" t="n">
-        <v>0.9567</v>
+        <v>0.9571</v>
       </c>
       <c r="O194" s="4" t="inlineStr"/>
       <c r="P194" s="4" t="inlineStr"/>
@@ -10974,12 +11090,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>QBYNBG1</t>
+          <t>RIVNBG2</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Queanbeyan BESS</t>
+          <t>Riverina Energy Storage System 2</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -10988,7 +11104,7 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="E195" s="4" t="inlineStr"/>
       <c r="F195" s="4" t="inlineStr"/>
@@ -10998,13 +11114,13 @@
       <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr"/>
       <c r="L195" s="4" t="n">
-        <v>0.9752</v>
+        <v>0.9058</v>
       </c>
       <c r="M195" s="4" t="n">
-        <v>0.979</v>
+        <v>0.9106</v>
       </c>
       <c r="N195" s="4" t="n">
-        <v>0.9571</v>
+        <v>0.9048</v>
       </c>
       <c r="O195" s="4" t="inlineStr"/>
       <c r="P195" s="4" t="inlineStr"/>
@@ -11014,12 +11130,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>RESS1G</t>
+          <t>DPNTBG1</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Riverina BESS 1</t>
+          <t>Darlington Point Energy Storage System</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -11028,7 +11144,7 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E196" s="4" t="inlineStr"/>
       <c r="F196" s="4" t="inlineStr"/>
@@ -11038,13 +11154,13 @@
       <c r="J196" s="4" t="inlineStr"/>
       <c r="K196" s="4" t="inlineStr"/>
       <c r="L196" s="4" t="n">
-        <v>0.9286</v>
+        <v>0.9402</v>
       </c>
       <c r="M196" s="4" t="n">
         <v>0.9089</v>
       </c>
       <c r="N196" s="4" t="n">
-        <v>0.8702</v>
+        <v>0.9048</v>
       </c>
       <c r="O196" s="4" t="inlineStr"/>
       <c r="P196" s="4" t="inlineStr"/>
@@ -11054,12 +11170,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>RIVNBG2</t>
+          <t>RESS1G</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Riverina Energy Storage System 2</t>
+          <t>Riverina BESS 1</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -11068,7 +11184,7 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E197" s="4" t="inlineStr"/>
       <c r="F197" s="4" t="inlineStr"/>
@@ -11078,13 +11194,13 @@
       <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr"/>
       <c r="L197" s="4" t="n">
-        <v>0.9058</v>
+        <v>0.9286</v>
       </c>
       <c r="M197" s="4" t="n">
-        <v>0.9106</v>
+        <v>0.9089</v>
       </c>
       <c r="N197" s="4" t="n">
-        <v>0.9048</v>
+        <v>0.8702</v>
       </c>
       <c r="O197" s="4" t="inlineStr"/>
       <c r="P197" s="4" t="inlineStr"/>
@@ -11094,96 +11210,58 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CAPBES1G</t>
+          <t>WESTCBT1</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Capital Battery</t>
+          <t>Western Suburbs League Club (Campbelltown) Plant</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="E198" s="4" t="inlineStr"/>
-      <c r="F198" s="4" t="inlineStr"/>
-      <c r="G198" s="4" t="inlineStr"/>
-      <c r="H198" s="4" t="inlineStr"/>
-      <c r="I198" s="4" t="inlineStr"/>
-      <c r="J198" s="4" t="inlineStr"/>
-      <c r="K198" s="4" t="inlineStr"/>
-      <c r="L198" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>1.0005</v>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="H198" s="4" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="I198" s="4" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="J198" s="4" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="K198" s="4" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="L198" s="4" t="n">
+        <v>0.9976</v>
+      </c>
       <c r="M198" s="4" t="n">
-        <v>0.9704</v>
+        <v>0.9958</v>
       </c>
       <c r="N198" s="4" t="n">
-        <v>0.9337</v>
-      </c>
-      <c r="O198" s="4" t="inlineStr"/>
+        <v>0.9954</v>
+      </c>
+      <c r="O198" s="4" t="n">
+        <v>0.9961</v>
+      </c>
       <c r="P198" s="4" t="inlineStr"/>
       <c r="Q198" s="4" t="inlineStr"/>
       <c r="R198" s="5" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>WESTCBT1</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>Western Suburbs League Club (Campbelltown) Plant</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="4" t="n">
-        <v>0.9991</v>
-      </c>
-      <c r="F199" s="4" t="n">
-        <v>1.0005</v>
-      </c>
-      <c r="G199" s="4" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="H199" s="4" t="n">
-        <v>1.0006</v>
-      </c>
-      <c r="I199" s="4" t="n">
-        <v>0.9973</v>
-      </c>
-      <c r="J199" s="4" t="n">
-        <v>0.9983</v>
-      </c>
-      <c r="K199" s="4" t="n">
-        <v>0.9987</v>
-      </c>
-      <c r="L199" s="4" t="n">
-        <v>0.9976</v>
-      </c>
-      <c r="M199" s="4" t="n">
-        <v>0.9958</v>
-      </c>
-      <c r="N199" s="4" t="n">
-        <v>0.9954</v>
-      </c>
-      <c r="O199" s="4" t="n">
-        <v>0.9961</v>
-      </c>
-      <c r="P199" s="4" t="inlineStr"/>
-      <c r="Q199" s="4" t="inlineStr"/>
-      <c r="R199" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11196,7 +11274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11352,12 +11430,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WRSF1</t>
+          <t>WRWF1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
       <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>0.8468</v>
+      </c>
       <c r="E4" s="4" t="n">
         <v>0.8427</v>
       </c>
@@ -11389,14 +11469,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WRWF1</t>
+          <t>WRSF1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr"/>
       <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="n">
-        <v>0.8468</v>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="n">
         <v>0.8427</v>
       </c>
@@ -11729,7 +11807,9 @@
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="n">
+        <v>0.928</v>
+      </c>
       <c r="M14" s="4" t="n">
         <v>0.8568</v>
       </c>
@@ -12218,7 +12298,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NEWENSF1</t>
+          <t>NEWENSF2</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr"/>
@@ -12247,7 +12327,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NEWENSF2</t>
+          <t>NEWENSF1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr"/>
@@ -12362,8 +12442,12 @@
       <c r="H34" s="4" t="inlineStr"/>
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="n">
+        <v>0.8284</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.9484</v>
+      </c>
       <c r="M34" s="4" t="n">
         <v>0.892</v>
       </c>
@@ -12521,8 +12605,12 @@
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="n">
+        <v>0.8657</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.9396</v>
+      </c>
       <c r="M39" s="4" t="n">
         <v>0.9008</v>
       </c>
@@ -12530,7 +12618,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>QPSFB1</t>
+          <t>QPSFB2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr"/>
@@ -12553,7 +12641,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QPSFB2</t>
+          <t>QPSFB1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr"/>
@@ -12566,7 +12654,9 @@
       <c r="I41" s="4" t="inlineStr"/>
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
+        <v>1.019</v>
+      </c>
       <c r="M41" s="4" t="n">
         <v>0.9032</v>
       </c>
@@ -12586,8 +12676,12 @@
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.9453</v>
+      </c>
       <c r="M42" s="4" t="n">
         <v>0.9085</v>
       </c>
@@ -12638,8 +12732,12 @@
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.9443</v>
+      </c>
       <c r="M44" s="4" t="n">
         <v>0.9102</v>
       </c>
@@ -12690,7 +12788,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NESBESS1</t>
+          <t>NESBESS2</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr"/>
@@ -12703,7 +12801,9 @@
       <c r="I46" s="4" t="inlineStr"/>
       <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="n">
+        <v>0.8903</v>
+      </c>
       <c r="M46" s="4" t="n">
         <v>0.9197</v>
       </c>
@@ -12711,7 +12811,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NESBESS2</t>
+          <t>NESBESS1</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr"/>
@@ -12724,7 +12824,9 @@
       <c r="I47" s="4" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="n">
+        <v>0.8903</v>
+      </c>
       <c r="M47" s="4" t="n">
         <v>0.9197</v>
       </c>
@@ -12775,7 +12877,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>URANQ12</t>
+          <t>URANQ11</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
@@ -12818,7 +12920,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>URANQ13</t>
+          <t>URANQ12</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
@@ -12861,7 +12963,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>URANQ11</t>
+          <t>URANQ13</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
@@ -12974,31 +13076,41 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>WELLSF1</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr"/>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+          <t>GUTHEGA</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>0.9658</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.9016</v>
+      </c>
       <c r="G54" s="4" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9125</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.9444</v>
+        <v>0.9006</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0.9352</v>
+        <v>0.887</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.9439</v>
+        <v>0.893</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.9284</v>
+        <v>0.892</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.923</v>
+        <v>0.9135</v>
       </c>
       <c r="M54" s="4" t="n">
         <v>0.9273</v>
@@ -13007,41 +13119,31 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GUTHEGA</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n">
-        <v>0.8882</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>0.9371</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>0.9658</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>0.9016</v>
-      </c>
+          <t>WELLSF1</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
-        <v>0.9125</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0.9006</v>
+        <v>0.9444</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.887</v>
+        <v>0.9352</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.893</v>
+        <v>0.9439</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0.892</v>
+        <v>0.9284</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.9135</v>
+        <v>0.923</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>0.9273</v>
@@ -13050,15 +13152,19 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NEVERSF1</t>
+          <t>NASF1</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr"/>
       <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.9708</v>
+      </c>
       <c r="F56" s="4" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9603</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>0.9569</v>
@@ -13085,19 +13191,15 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>NASF1</t>
+          <t>NEVERSF1</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr"/>
       <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="n">
-        <v>0.9714</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>0.9708</v>
-      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="n">
-        <v>0.9603</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>0.9569</v>
@@ -13299,7 +13401,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>STUBSF2</t>
+          <t>STUBSF1</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr"/>
@@ -13324,7 +13426,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>STUBSF1</t>
+          <t>STUBSF2</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr"/>
@@ -13603,7 +13705,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GUNNING1</t>
+          <t>CULLRGWF</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
@@ -13646,7 +13748,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>CULLRGWF</t>
+          <t>GUNNING1</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
@@ -13710,7 +13812,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HUNTER1</t>
+          <t>HUNTER2</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr"/>
@@ -13735,7 +13837,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HUNTER2</t>
+          <t>HUNTER1</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr"/>
@@ -13810,7 +13912,9 @@
       <c r="I77" s="4" t="inlineStr"/>
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
+      <c r="L77" s="4" t="n">
+        <v>0.9737</v>
+      </c>
       <c r="M77" s="4" t="n">
         <v>0.955</v>
       </c>
@@ -14032,7 +14136,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>BW03</t>
+          <t>BW04</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
@@ -14075,7 +14179,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BW04</t>
+          <t>BW03</t>
         </is>
       </c>
       <c r="B85" s="4" t="n">
@@ -14118,7 +14222,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BW02</t>
+          <t>BW01</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
@@ -14161,7 +14265,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>BW01</t>
+          <t>BW02</t>
         </is>
       </c>
       <c r="B87" s="4" t="n">
@@ -14204,13 +14308,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GULLRWF2</t>
+          <t>GULLRSF1</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr"/>
       <c r="C88" s="4" t="inlineStr"/>
-      <c r="D88" s="4" t="inlineStr"/>
-      <c r="E88" s="4" t="inlineStr"/>
+      <c r="D88" s="4" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0.9959</v>
+      </c>
       <c r="F88" s="4" t="n">
         <v>0.9694</v>
       </c>
@@ -14239,17 +14347,13 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GULLRSF1</t>
+          <t>GULLRWF2</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr"/>
       <c r="C89" s="4" t="inlineStr"/>
-      <c r="D89" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>0.9959</v>
-      </c>
+      <c r="D89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="n">
         <v>0.9694</v>
       </c>
@@ -14560,7 +14664,9 @@
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="4" t="inlineStr"/>
+      <c r="L97" s="4" t="n">
+        <v>0.9643</v>
+      </c>
       <c r="M97" s="4" t="n">
         <v>0.9675</v>
       </c>
@@ -14953,7 +15059,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GLENNCRK</t>
+          <t>GLBWNHYD</t>
         </is>
       </c>
       <c r="B107" s="4" t="n">
@@ -14996,7 +15102,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GLBWNHYD</t>
+          <t>GLENNCRK</t>
         </is>
       </c>
       <c r="B108" s="4" t="n">
@@ -15082,7 +15188,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1-3</t>
+          <t>TUMUT1-1</t>
         </is>
       </c>
       <c r="B110" s="4" t="n">
@@ -15125,7 +15231,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1-1</t>
+          <t>TUMUT1-3</t>
         </is>
       </c>
       <c r="B111" s="4" t="n">
@@ -15168,7 +15274,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TUMUT1-4</t>
+          <t>TUMUT2-4</t>
         </is>
       </c>
       <c r="B112" s="4" t="n">
@@ -15211,7 +15317,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-1</t>
+          <t>TUMUT2-2</t>
         </is>
       </c>
       <c r="B113" s="4" t="n">
@@ -15254,7 +15360,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-2</t>
+          <t>TUMUT2-1</t>
         </is>
       </c>
       <c r="B114" s="4" t="n">
@@ -15297,7 +15403,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-3</t>
+          <t>TUMUT1-4</t>
         </is>
       </c>
       <c r="B115" s="4" t="n">
@@ -15340,7 +15446,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TUMUT2-4</t>
+          <t>TUMUT2-3</t>
         </is>
       </c>
       <c r="B116" s="4" t="n">
@@ -15383,7 +15489,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>CG2</t>
+          <t>CG4</t>
         </is>
       </c>
       <c r="B117" s="4" t="n">
@@ -15469,7 +15575,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>CG3</t>
+          <t>CG2</t>
         </is>
       </c>
       <c r="B119" s="4" t="n">
@@ -15512,7 +15618,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>CG4</t>
+          <t>CG3</t>
         </is>
       </c>
       <c r="B120" s="4" t="n">
@@ -15598,29 +15704,41 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>HEZ1</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr"/>
-      <c r="C122" s="4" t="inlineStr"/>
-      <c r="D122" s="4" t="inlineStr"/>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="4" t="inlineStr"/>
+          <t>ERGT01</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="n">
+        <v>0.9856</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0.9835</v>
+      </c>
       <c r="H122" s="4" t="n">
-        <v>0.9897</v>
+        <v>0.9849</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>0.992</v>
+        <v>0.9865</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>0.9899</v>
+        <v>0.9848</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.9896</v>
+        <v>0.9855</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.9931</v>
+        <v>0.9846</v>
       </c>
       <c r="M122" s="4" t="n">
         <v>0.9831</v>
@@ -15672,41 +15790,29 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ERGT01</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="n">
-        <v>0.9856</v>
-      </c>
-      <c r="C124" s="4" t="n">
-        <v>0.9829</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="E124" s="4" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="F124" s="4" t="n">
-        <v>0.9836</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>0.9835</v>
-      </c>
+          <t>HEZ1</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr"/>
+      <c r="C124" s="4" t="inlineStr"/>
+      <c r="D124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
+      <c r="G124" s="4" t="inlineStr"/>
       <c r="H124" s="4" t="n">
-        <v>0.9849</v>
+        <v>0.9897</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>0.9865</v>
+        <v>0.992</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>0.9848</v>
+        <v>0.9899</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0.9855</v>
+        <v>0.9896</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.9846</v>
+        <v>0.9931</v>
       </c>
       <c r="M124" s="4" t="n">
         <v>0.9831</v>
@@ -15758,7 +15864,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ER03</t>
+          <t>ER04</t>
         </is>
       </c>
       <c r="B126" s="4" t="n">
@@ -15801,7 +15907,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ER04</t>
+          <t>ER03</t>
         </is>
       </c>
       <c r="B127" s="4" t="n">
@@ -15887,7 +15993,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>VPNL1</t>
+          <t>VP5</t>
         </is>
       </c>
       <c r="B129" s="4" t="n">
@@ -15930,7 +16036,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>VP5</t>
+          <t>VPNL1</t>
         </is>
       </c>
       <c r="B130" s="4" t="n">
@@ -15973,7 +16079,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>JOUNAMA1</t>
+          <t>TUMT3NL3</t>
         </is>
       </c>
       <c r="B131" s="4" t="n">
@@ -16016,7 +16122,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL1</t>
+          <t>TUMT3NL2</t>
         </is>
       </c>
       <c r="B132" s="4" t="n">
@@ -16059,7 +16165,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL2</t>
+          <t>TUMT3NL1</t>
         </is>
       </c>
       <c r="B133" s="4" t="n">
@@ -16102,7 +16208,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL3</t>
+          <t>JOUNAMA1</t>
         </is>
       </c>
       <c r="B134" s="4" t="n">
@@ -16178,8 +16284,12 @@
       <c r="H136" s="4" t="inlineStr"/>
       <c r="I136" s="4" t="inlineStr"/>
       <c r="J136" s="4" t="inlineStr"/>
-      <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>0.9901</v>
+      </c>
       <c r="M136" s="4" t="n">
         <v>0.9903</v>
       </c>
@@ -16499,135 +16609,161 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>MLB01</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr"/>
-      <c r="C145" s="4" t="inlineStr"/>
-      <c r="D145" s="4" t="inlineStr"/>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
-      <c r="G145" s="4" t="inlineStr"/>
-      <c r="H145" s="4" t="inlineStr"/>
-      <c r="I145" s="4" t="inlineStr"/>
-      <c r="J145" s="4" t="inlineStr"/>
-      <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="4" t="inlineStr"/>
+          <t>THEDROP1</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>1.0157</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>1.1256</v>
+      </c>
+      <c r="E145" s="4" t="n">
+        <v>1.1441</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>0.9895</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="H145" s="4" t="n">
+        <v>0.9686</v>
+      </c>
+      <c r="I145" s="4" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="J145" s="4" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="K145" s="4" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="L145" s="4" t="n">
+        <v>0.9712</v>
+      </c>
       <c r="M145" s="4" t="n">
-        <v>0.994</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>THEDROP1</t>
+          <t>APPIN</t>
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>0.967</v>
+        <v>0.9998</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1.0157</v>
+        <v>0.9986</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>1.1256</v>
+        <v>1</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>1.1441</v>
+        <v>1.001</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>0.9895</v>
+        <v>0.9953</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>0.9537</v>
+        <v>0.9978</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>0.9686</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0.9708</v>
+        <v>0.9973</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>0.9687</v>
+        <v>0.995</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0.9563</v>
+        <v>0.9929</v>
       </c>
       <c r="L146" s="4" t="n">
-        <v>0.9712</v>
+        <v>0.995</v>
       </c>
       <c r="M146" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>APPIN</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="C147" s="4" t="n">
-        <v>0.9986</v>
-      </c>
-      <c r="D147" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="F147" s="4" t="n">
-        <v>0.9953</v>
-      </c>
-      <c r="G147" s="4" t="n">
-        <v>0.9978</v>
-      </c>
-      <c r="H147" s="4" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="I147" s="4" t="n">
-        <v>0.9973</v>
-      </c>
-      <c r="J147" s="4" t="n">
-        <v>0.995</v>
-      </c>
+          <t>WTAHB1</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr"/>
+      <c r="C147" s="4" t="inlineStr"/>
+      <c r="D147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.997</v>
       </c>
       <c r="L147" s="4" t="n">
-        <v>0.995</v>
+        <v>0.9923</v>
       </c>
       <c r="M147" s="4" t="n">
-        <v>0.9948</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>WTAHB1</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr"/>
-      <c r="C148" s="4" t="inlineStr"/>
-      <c r="D148" s="4" t="inlineStr"/>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
-      <c r="G148" s="4" t="inlineStr"/>
-      <c r="H148" s="4" t="inlineStr"/>
-      <c r="I148" s="4" t="inlineStr"/>
-      <c r="J148" s="4" t="inlineStr"/>
-      <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr"/>
+          <t>WYANGALB</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="n">
+        <v>1.0099</v>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>1.0355</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>1.0435</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>1.0411</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>1.0314</v>
+      </c>
+      <c r="G148" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="H148" s="4" t="n">
+        <v>0.9721</v>
+      </c>
+      <c r="I148" s="4" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="K148" s="4" t="n">
+        <v>0.9971</v>
+      </c>
+      <c r="L148" s="4" t="n">
+        <v>0.9858</v>
+      </c>
       <c r="M148" s="4" t="n">
-        <v>0.9972</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>WYANGALB</t>
+          <t>WYANGALA</t>
         </is>
       </c>
       <c r="B149" s="4" t="n">
@@ -16670,65 +16806,69 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>WYANGALA</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="n">
-        <v>1.0099</v>
-      </c>
-      <c r="C150" s="4" t="n">
-        <v>1.0355</v>
-      </c>
-      <c r="D150" s="4" t="n">
-        <v>1.0435</v>
-      </c>
-      <c r="E150" s="4" t="n">
-        <v>1.0411</v>
-      </c>
-      <c r="F150" s="4" t="n">
-        <v>1.0314</v>
-      </c>
-      <c r="G150" s="4" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="H150" s="4" t="n">
-        <v>0.9721</v>
-      </c>
-      <c r="I150" s="4" t="n">
-        <v>0.9746</v>
-      </c>
-      <c r="J150" s="4" t="n">
-        <v>0.9378</v>
-      </c>
+          <t>QBYNB1</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr"/>
+      <c r="C150" s="4" t="inlineStr"/>
+      <c r="D150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
+      <c r="G150" s="4" t="inlineStr"/>
+      <c r="H150" s="4" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="n">
-        <v>0.9971</v>
+        <v>0.9795</v>
       </c>
       <c r="L150" s="4" t="n">
-        <v>0.9858</v>
+        <v>1.0072</v>
       </c>
       <c r="M150" s="4" t="n">
-        <v>0.998</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>QBYNB1</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr"/>
-      <c r="C151" s="4" t="inlineStr"/>
-      <c r="D151" s="4" t="inlineStr"/>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
-      <c r="G151" s="4" t="inlineStr"/>
-      <c r="H151" s="4" t="inlineStr"/>
-      <c r="I151" s="4" t="inlineStr"/>
-      <c r="J151" s="4" t="inlineStr"/>
-      <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="4" t="inlineStr"/>
+          <t>LUCAS2S2</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>1.0029</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="H151" s="4" t="n">
+        <v>1.0015</v>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="K151" s="4" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="L151" s="4" t="n">
+        <v>0.9987</v>
+      </c>
       <c r="M151" s="4" t="n">
-        <v>0.9982</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="152">
@@ -16777,97 +16917,97 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>LUCAS2S2</t>
+          <t>GRANGEAV</t>
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>1.0016</v>
+        <v>0.9996</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>1.0029</v>
+        <v>0.9991</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>1.0033</v>
+        <v>0.9989</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1.0036</v>
+        <v>0.9991</v>
       </c>
       <c r="F153" s="4" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="4" t="n">
         <v>1.0001</v>
       </c>
-      <c r="G153" s="4" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="H153" s="4" t="n">
-        <v>1.0015</v>
-      </c>
-      <c r="I153" s="4" t="n">
-        <v>1.0009</v>
-      </c>
       <c r="J153" s="4" t="n">
-        <v>0.9988</v>
+        <v>0.9998</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0.9984</v>
+        <v>0.9998</v>
       </c>
       <c r="L153" s="4" t="n">
-        <v>0.9987</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="M153" s="4" t="n">
-        <v>0.9983</v>
+        <v>0.9993</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GRANGEAV</t>
+          <t>TOWER</t>
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>0.9996</v>
+        <v>1.002</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>0.9991</v>
+        <v>1.0019</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>0.9989</v>
+        <v>1.0022</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>0.9991</v>
+        <v>1.0024</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>0.9997</v>
+        <v>1.0009</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>0.9997</v>
+        <v>1.0012</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>1</v>
+        <v>1.0015</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.0011</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="K154" s="4" t="n">
         <v>0.9998</v>
       </c>
       <c r="L154" s="4" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="M154" s="4" t="n">
-        <v>0.9993</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>TOWER</t>
+          <t>TAHMOOR1</t>
         </is>
       </c>
       <c r="B155" s="4" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="C155" s="4" t="n">
         <v>1.0019</v>
@@ -16906,173 +17046,173 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>TAHMOOR1</t>
+          <t>DG_NSW1</t>
         </is>
       </c>
       <c r="B156" s="4" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="C156" s="4" t="n">
-        <v>1.0019</v>
+        <v>1</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>1.0022</v>
+        <v>1</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1.0024</v>
+        <v>1</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1.0009</v>
+        <v>1</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>1.0012</v>
+        <v>1</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>1.0015</v>
+        <v>1</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>1.0011</v>
+        <v>1</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="L156" s="4" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="M156" s="4" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>DG_NSW1</t>
+          <t>STGEORG1</t>
         </is>
       </c>
       <c r="B157" s="4" t="n">
-        <v>1</v>
+        <v>1.0059</v>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1</v>
+        <v>1.0071</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>1</v>
+        <v>1.0069</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>1</v>
+        <v>1.0063</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>1</v>
+        <v>1.003</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>1</v>
+        <v>1.0035</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>1</v>
+        <v>1.0045</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>1</v>
+        <v>1.0037</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>1</v>
+        <v>1.0013</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>1.0009</v>
       </c>
       <c r="L157" s="4" t="n">
-        <v>1</v>
+        <v>1.0013</v>
       </c>
       <c r="M157" s="4" t="n">
-        <v>1</v>
+        <v>1.0008</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>STGEORG1</t>
+          <t>SITHE01</t>
         </is>
       </c>
       <c r="B158" s="4" t="n">
-        <v>1.0059</v>
+        <v>1.0018</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>1.0071</v>
+        <v>1.0035</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>1.0069</v>
+        <v>1.0041</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>1.0063</v>
+        <v>1</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>1.003</v>
+        <v>1.0029</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>1.0035</v>
+        <v>1.0025</v>
       </c>
       <c r="H158" s="4" t="n">
-        <v>1.0045</v>
+        <v>1.0017</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>1.0037</v>
+        <v>1.0018</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>1.0013</v>
+        <v>1.0015</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1.0009</v>
+        <v>1.0015</v>
       </c>
       <c r="L158" s="4" t="n">
-        <v>1.0013</v>
+        <v>1.0017</v>
       </c>
       <c r="M158" s="4" t="n">
-        <v>1.0008</v>
+        <v>1.0015</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SITHE01</t>
+          <t>EASTCRK2</t>
         </is>
       </c>
       <c r="B159" s="4" t="n">
-        <v>1.0018</v>
+        <v>1.0021</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>1.0035</v>
+        <v>1.0021</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>1.0041</v>
+        <v>1.0021</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1</v>
+        <v>1.0021</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.0021</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>1.0025</v>
+        <v>1.001</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>1.0017</v>
+        <v>1.001</v>
       </c>
       <c r="I159" s="4" t="n">
-        <v>1.0018</v>
+        <v>1.001</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>1.0015</v>
+        <v>1.001</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1.0015</v>
+        <v>1.001</v>
       </c>
       <c r="L159" s="4" t="n">
-        <v>1.0017</v>
+        <v>1.0016</v>
       </c>
       <c r="M159" s="4" t="n">
-        <v>1.0015</v>
+        <v>1.0016</v>
       </c>
     </row>
     <row r="160">
@@ -17121,50 +17261,32 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>EASTCRK2</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="D161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="F161" s="4" t="n">
-        <v>1.0021</v>
-      </c>
-      <c r="G161" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="H161" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="I161" s="4" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="J161" s="4" t="n">
-        <v>1.001</v>
-      </c>
+          <t>WALGRV1</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr"/>
+      <c r="C161" s="4" t="inlineStr"/>
+      <c r="D161" s="4" t="inlineStr"/>
+      <c r="E161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="inlineStr"/>
+      <c r="G161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="n">
-        <v>1.001</v>
+        <v>1.0009</v>
       </c>
       <c r="L161" s="4" t="n">
-        <v>1.0016</v>
+        <v>1.0015</v>
       </c>
       <c r="M161" s="4" t="n">
-        <v>1.0016</v>
+        <v>1.0017</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>WALGRV1</t>
+          <t>SMTHBES1</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr"/>
@@ -17177,73 +17299,97 @@
       <c r="I162" s="4" t="inlineStr"/>
       <c r="J162" s="4" t="inlineStr"/>
       <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="4" t="inlineStr"/>
+      <c r="L162" s="4" t="n">
+        <v>1.0017</v>
+      </c>
       <c r="M162" s="4" t="n">
-        <v>1.0017</v>
+        <v>1.0019</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SMTHBES1</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr"/>
-      <c r="C163" s="4" t="inlineStr"/>
-      <c r="D163" s="4" t="inlineStr"/>
-      <c r="E163" s="4" t="inlineStr"/>
-      <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr"/>
-      <c r="H163" s="4" t="inlineStr"/>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
-      <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr"/>
+          <t>CESF1</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n">
+        <v>0.9923999999999999</v>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>1.0257</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>1.0563</v>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>1.0438</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="G163" s="4" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="H163" s="4" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="I163" s="4" t="n">
+        <v>0.9866</v>
+      </c>
+      <c r="J163" s="4" t="n">
+        <v>0.9867</v>
+      </c>
+      <c r="K163" s="4" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="L163" s="4" t="n">
+        <v>0.9954</v>
+      </c>
       <c r="M163" s="4" t="n">
-        <v>1.0019</v>
+        <v>1.0026</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>CESF1</t>
+          <t>TARALGA1</t>
         </is>
       </c>
       <c r="B164" s="4" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>1.0257</v>
+        <v>0.9922</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>1.0563</v>
+        <v>0.9998</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1.0438</v>
+        <v>0.9977</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>0.989</v>
+        <v>1.0086</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>0.9982</v>
+        <v>1.0103</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>0.9882</v>
+        <v>1.0122</v>
       </c>
       <c r="I164" s="4" t="n">
-        <v>0.9866</v>
+        <v>1.0118</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>0.9867</v>
+        <v>1.0095</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0.9751</v>
+        <v>1.0088</v>
       </c>
       <c r="L164" s="4" t="n">
-        <v>0.9954</v>
+        <v>0.9971</v>
       </c>
       <c r="M164" s="4" t="n">
-        <v>1.0026</v>
+        <v>1.0029</v>
       </c>
     </row>
     <row r="165">
@@ -17292,120 +17438,120 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TARALGA1</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="n">
-        <v>0.9844000000000001</v>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="F166" s="4" t="n">
-        <v>1.0086</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>1.0103</v>
-      </c>
-      <c r="H166" s="4" t="n">
-        <v>1.0122</v>
-      </c>
-      <c r="I166" s="4" t="n">
-        <v>1.0118</v>
-      </c>
+          <t>FLYCRKWF</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr"/>
+      <c r="C166" s="4" t="inlineStr"/>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr"/>
+      <c r="F166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr"/>
       <c r="J166" s="4" t="n">
-        <v>1.0095</v>
+        <v>1.0266</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>1.0088</v>
+        <v>1.0205</v>
       </c>
       <c r="L166" s="4" t="n">
-        <v>0.9971</v>
+        <v>1.0278</v>
       </c>
       <c r="M166" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.0047</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>FLYCRKWF</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr"/>
-      <c r="C167" s="4" t="inlineStr"/>
-      <c r="D167" s="4" t="inlineStr"/>
-      <c r="E167" s="4" t="inlineStr"/>
-      <c r="F167" s="4" t="inlineStr"/>
-      <c r="G167" s="4" t="inlineStr"/>
-      <c r="H167" s="4" t="inlineStr"/>
-      <c r="I167" s="4" t="inlineStr"/>
+          <t>GUTHNL1</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="n">
+        <v>0.9549</v>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>1.0148</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>1.0426</v>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>1.0256</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="H167" s="4" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="I167" s="4" t="n">
+        <v>0.9633</v>
+      </c>
       <c r="J167" s="4" t="n">
-        <v>1.0266</v>
+        <v>0.9838</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1.0205</v>
+        <v>0.9795</v>
       </c>
       <c r="L167" s="4" t="n">
-        <v>1.0278</v>
+        <v>1.0003</v>
       </c>
       <c r="M167" s="4" t="n">
-        <v>1.0047</v>
+        <v>1.0048</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GUTHNL1</t>
+          <t>TUMUT3-5</t>
         </is>
       </c>
       <c r="B168" s="4" t="n">
-        <v>0.9549</v>
+        <v>1.0092</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>1.0148</v>
+        <v>1.0092</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>1.0426</v>
+        <v>1.0092</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>1.0256</v>
+        <v>1.0092</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>0.9922</v>
+        <v>1.0092</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>0.9865</v>
+        <v>1.0092</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>0.9762</v>
+        <v>1.0092</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>0.9633</v>
+        <v>1.0092</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>0.9838</v>
+        <v>1.0092</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0.9795</v>
+        <v>1.0092</v>
       </c>
       <c r="L168" s="4" t="n">
-        <v>1.0003</v>
+        <v>1.0092</v>
       </c>
       <c r="M168" s="4" t="n">
-        <v>1.0048</v>
+        <v>1.0092</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-1</t>
+          <t>TUMUT3-4</t>
         </is>
       </c>
       <c r="B169" s="4" t="n">
@@ -17448,7 +17594,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-3</t>
+          <t>TUMUT3-6</t>
         </is>
       </c>
       <c r="B170" s="4" t="n">
@@ -17491,7 +17637,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-4</t>
+          <t>TUMUT3-2</t>
         </is>
       </c>
       <c r="B171" s="4" t="n">
@@ -17534,7 +17680,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-5</t>
+          <t>TUMUT3-1</t>
         </is>
       </c>
       <c r="B172" s="4" t="n">
@@ -17577,7 +17723,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-6</t>
+          <t>TUMUT3-3</t>
         </is>
       </c>
       <c r="B173" s="4" t="n">
@@ -17620,53 +17766,37 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TUMUT3-2</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="D174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="E174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="F174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="G174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="H174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="I174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
-      <c r="J174" s="4" t="n">
-        <v>1.0092</v>
-      </c>
+          <t>CAPBES1</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr"/>
+      <c r="C174" s="4" t="inlineStr"/>
+      <c r="D174" s="4" t="inlineStr"/>
+      <c r="E174" s="4" t="inlineStr"/>
+      <c r="F174" s="4" t="inlineStr"/>
+      <c r="G174" s="4" t="inlineStr"/>
+      <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr"/>
+      <c r="J174" s="4" t="inlineStr"/>
       <c r="K174" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0084</v>
       </c>
       <c r="L174" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0389</v>
       </c>
       <c r="M174" s="4" t="n">
-        <v>1.0092</v>
+        <v>1.0263</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>CAPBES1</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr"/>
+          <t>REDBANK1</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="n">
+        <v>0.9843</v>
+      </c>
       <c r="C175" s="4" t="inlineStr"/>
       <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="4" t="inlineStr"/>
@@ -17677,20 +17807,20 @@
       <c r="J175" s="4" t="inlineStr"/>
       <c r="K175" s="4" t="inlineStr"/>
       <c r="L175" s="4" t="inlineStr"/>
-      <c r="M175" s="4" t="n">
-        <v>1.0263</v>
-      </c>
+      <c r="M175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>REDBANK1</t>
+          <t>HEZ</t>
         </is>
       </c>
       <c r="B176" s="4" t="n">
-        <v>0.9843</v>
-      </c>
-      <c r="C176" s="4" t="inlineStr"/>
+        <v>0.9969</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>0.9967</v>
+      </c>
       <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr"/>
       <c r="F176" s="4" t="inlineStr"/>
@@ -17705,16 +17835,18 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>HEZ</t>
+          <t>BANKSPT1</t>
         </is>
       </c>
       <c r="B177" s="4" t="n">
-        <v>0.9969</v>
+        <v>1.0016</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>0.9967</v>
-      </c>
-      <c r="D177" s="4" t="inlineStr"/>
+        <v>1.0029</v>
+      </c>
+      <c r="D177" s="4" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="E177" s="4" t="inlineStr"/>
       <c r="F177" s="4" t="inlineStr"/>
       <c r="G177" s="4" t="inlineStr"/>
@@ -17728,19 +17860,21 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>BANKSPT1</t>
+          <t>AWABAREF</t>
         </is>
       </c>
       <c r="B178" s="4" t="n">
-        <v>1.0016</v>
+        <v>0.9926</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1.0029</v>
+        <v>0.9907</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>1.0033</v>
-      </c>
-      <c r="E178" s="4" t="inlineStr"/>
+        <v>0.9892</v>
+      </c>
+      <c r="E178" s="4" t="n">
+        <v>0.9901</v>
+      </c>
       <c r="F178" s="4" t="inlineStr"/>
       <c r="G178" s="4" t="inlineStr"/>
       <c r="H178" s="4" t="inlineStr"/>
@@ -17753,23 +17887,27 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AWABAREF</t>
+          <t>NINEWIL1</t>
         </is>
       </c>
       <c r="B179" s="4" t="n">
-        <v>0.9926</v>
+        <v>1.0051</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>0.9907</v>
+        <v>1.005</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>0.9892</v>
+        <v>1.0048</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>0.9901</v>
-      </c>
-      <c r="F179" s="4" t="inlineStr"/>
-      <c r="G179" s="4" t="inlineStr"/>
+        <v>1.0049</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="G179" s="4" t="n">
+        <v>1.0058</v>
+      </c>
       <c r="H179" s="4" t="inlineStr"/>
       <c r="I179" s="4" t="inlineStr"/>
       <c r="J179" s="4" t="inlineStr"/>
@@ -17780,28 +17918,30 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>NINEWIL1</t>
+          <t>TERALBA</t>
         </is>
       </c>
       <c r="B180" s="4" t="n">
-        <v>1.0051</v>
+        <v>0.9926</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1.005</v>
+        <v>0.9907</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>1.0048</v>
+        <v>0.9892</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>1.0049</v>
+        <v>0.9901</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>1.007</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>1.0058</v>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
+        <v>0.9907</v>
+      </c>
+      <c r="H180" s="4" t="n">
+        <v>0.9917</v>
+      </c>
       <c r="I180" s="4" t="inlineStr"/>
       <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr"/>
@@ -17844,29 +17984,29 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TERALBA</t>
+          <t>HVGTS</t>
         </is>
       </c>
       <c r="B182" s="4" t="n">
-        <v>0.9926</v>
+        <v>0.974</v>
       </c>
       <c r="C182" s="4" t="n">
-        <v>0.9907</v>
+        <v>0.9679</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>0.9892</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>0.9901</v>
+        <v>0.9596</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9654</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>0.9907</v>
+        <v>0.9673</v>
       </c>
       <c r="H182" s="4" t="n">
-        <v>0.9917</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="I182" s="4" t="inlineStr"/>
       <c r="J182" s="4" t="inlineStr"/>
@@ -17877,29 +18017,27 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>KINCUM1</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="n">
-        <v>1.0017</v>
-      </c>
+          <t>AGLSITA1</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr"/>
       <c r="C183" s="4" t="n">
+        <v>1.0019</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>1.0024</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>1.0009</v>
+      </c>
+      <c r="G183" s="4" t="n">
+        <v>1.0012</v>
+      </c>
+      <c r="H183" s="4" t="n">
         <v>1.0015</v>
-      </c>
-      <c r="D183" s="4" t="n">
-        <v>1.0008</v>
-      </c>
-      <c r="E183" s="4" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="F183" s="4" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="G183" s="4" t="n">
-        <v>1.0019</v>
-      </c>
-      <c r="H183" s="4" t="n">
-        <v>1.0037</v>
       </c>
       <c r="I183" s="4" t="inlineStr"/>
       <c r="J183" s="4" t="inlineStr"/>
@@ -17910,29 +18048,29 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>LD03</t>
+          <t>AGLNOW1</t>
         </is>
       </c>
       <c r="B184" s="4" t="n">
-        <v>0.9676</v>
+        <v>0.9916</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>0.9593</v>
+        <v>0.9986</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>0.9509</v>
+        <v>1.0023</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>0.9537</v>
+        <v>1.0037</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>0.9593</v>
+        <v>0.9929</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>0.9631</v>
+        <v>0.9967</v>
       </c>
       <c r="H184" s="4" t="n">
-        <v>0.9628</v>
+        <v>0.9929</v>
       </c>
       <c r="I184" s="4" t="inlineStr"/>
       <c r="J184" s="4" t="inlineStr"/>
@@ -17943,29 +18081,29 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>HVGTS</t>
+          <t>KINCUM1</t>
         </is>
       </c>
       <c r="B185" s="4" t="n">
-        <v>0.974</v>
+        <v>1.0017</v>
       </c>
       <c r="C185" s="4" t="n">
-        <v>0.9679</v>
+        <v>1.0015</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>0.9582000000000001</v>
+        <v>1.0008</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>0.9596</v>
+        <v>1.0011</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>0.9654</v>
+        <v>1.0036</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>0.9673</v>
+        <v>1.0019</v>
       </c>
       <c r="H185" s="4" t="n">
-        <v>0.9651999999999999</v>
+        <v>1.0037</v>
       </c>
       <c r="I185" s="4" t="inlineStr"/>
       <c r="J185" s="4" t="inlineStr"/>
@@ -17976,29 +18114,29 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>AGLNOW1</t>
+          <t>LD03</t>
         </is>
       </c>
       <c r="B186" s="4" t="n">
-        <v>0.9916</v>
+        <v>0.9676</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>0.9986</v>
+        <v>0.9593</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>1.0023</v>
+        <v>0.9509</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>1.0037</v>
+        <v>0.9537</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.9593</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>0.9967</v>
+        <v>0.9631</v>
       </c>
       <c r="H186" s="4" t="n">
-        <v>0.9929</v>
+        <v>0.9628</v>
       </c>
       <c r="I186" s="4" t="inlineStr"/>
       <c r="J186" s="4" t="inlineStr"/>
@@ -18009,29 +18147,33 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>AGLSITA1</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr"/>
+          <t>LD04</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="n">
+        <v>0.9676</v>
+      </c>
       <c r="C187" s="4" t="n">
-        <v>1.0019</v>
+        <v>0.9593</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>1.0022</v>
+        <v>0.9509</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>1.0024</v>
+        <v>0.9537</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>1.0009</v>
+        <v>0.9593</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>1.0012</v>
+        <v>0.9631</v>
       </c>
       <c r="H187" s="4" t="n">
-        <v>1.0015</v>
-      </c>
-      <c r="I187" s="4" t="inlineStr"/>
+        <v>0.9628</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>0.9659</v>
+      </c>
       <c r="J187" s="4" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr"/>
       <c r="L187" s="4" t="inlineStr"/>
@@ -18040,7 +18182,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>LD01</t>
+          <t>LD02</t>
         </is>
       </c>
       <c r="B188" s="4" t="n">
@@ -18075,7 +18217,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>LD02</t>
+          <t>LD01</t>
         </is>
       </c>
       <c r="B189" s="4" t="n">
@@ -18110,42 +18252,34 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>LD04</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="n">
-        <v>0.9676</v>
-      </c>
-      <c r="C190" s="4" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="D190" s="4" t="n">
-        <v>0.9509</v>
-      </c>
-      <c r="E190" s="4" t="n">
-        <v>0.9537</v>
-      </c>
-      <c r="F190" s="4" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="G190" s="4" t="n">
-        <v>0.9631</v>
-      </c>
+          <t>WALGRVG1</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr"/>
+      <c r="C190" s="4" t="inlineStr"/>
+      <c r="D190" s="4" t="inlineStr"/>
+      <c r="E190" s="4" t="inlineStr"/>
+      <c r="F190" s="4" t="inlineStr"/>
+      <c r="G190" s="4" t="inlineStr"/>
       <c r="H190" s="4" t="n">
-        <v>0.9628</v>
+        <v>1.0011</v>
       </c>
       <c r="I190" s="4" t="n">
-        <v>0.9659</v>
-      </c>
-      <c r="J190" s="4" t="inlineStr"/>
-      <c r="K190" s="4" t="inlineStr"/>
+        <v>1.001</v>
+      </c>
+      <c r="J190" s="4" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="K190" s="4" t="n">
+        <v>1.001</v>
+      </c>
       <c r="L190" s="4" t="inlineStr"/>
       <c r="M190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>WALGRVG1</t>
+          <t>MLLFGEF1</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr"/>
@@ -18155,16 +18289,16 @@
       <c r="F191" s="4" t="inlineStr"/>
       <c r="G191" s="4" t="inlineStr"/>
       <c r="H191" s="4" t="n">
-        <v>1.0011</v>
+        <v>0.9683</v>
       </c>
       <c r="I191" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9687</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9663</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>1.001</v>
+        <v>0.9567</v>
       </c>
       <c r="L191" s="4" t="inlineStr"/>
       <c r="M191" s="4" t="inlineStr"/>
@@ -18172,7 +18306,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>DPNTBG1</t>
+          <t>BHBG1</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr"/>
@@ -18182,14 +18316,12 @@
       <c r="F192" s="4" t="inlineStr"/>
       <c r="G192" s="4" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr"/>
-      <c r="I192" s="4" t="n">
-        <v>0.9402</v>
-      </c>
+      <c r="I192" s="4" t="inlineStr"/>
       <c r="J192" s="4" t="n">
-        <v>0.9089</v>
+        <v>0.8671</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0.9048</v>
+        <v>0.8423</v>
       </c>
       <c r="L192" s="4" t="inlineStr"/>
       <c r="M192" s="4" t="inlineStr"/>
@@ -18197,7 +18329,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>BHBG1</t>
+          <t>CAPBES1G</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr"/>
@@ -18209,10 +18341,10 @@
       <c r="H193" s="4" t="inlineStr"/>
       <c r="I193" s="4" t="inlineStr"/>
       <c r="J193" s="4" t="n">
-        <v>0.8671</v>
+        <v>0.9704</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0.8423</v>
+        <v>0.9337</v>
       </c>
       <c r="L193" s="4" t="inlineStr"/>
       <c r="M193" s="4" t="inlineStr"/>
@@ -18220,7 +18352,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>MLLFGEF1</t>
+          <t>QBYNBG1</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr"/>
@@ -18229,17 +18361,15 @@
       <c r="E194" s="4" t="inlineStr"/>
       <c r="F194" s="4" t="inlineStr"/>
       <c r="G194" s="4" t="inlineStr"/>
-      <c r="H194" s="4" t="n">
-        <v>0.9683</v>
-      </c>
+      <c r="H194" s="4" t="inlineStr"/>
       <c r="I194" s="4" t="n">
-        <v>0.9687</v>
+        <v>0.9752</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>0.9663</v>
+        <v>0.979</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>0.9567</v>
+        <v>0.9571</v>
       </c>
       <c r="L194" s="4" t="inlineStr"/>
       <c r="M194" s="4" t="inlineStr"/>
@@ -18247,7 +18377,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>QBYNBG1</t>
+          <t>RIVNBG2</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr"/>
@@ -18258,13 +18388,13 @@
       <c r="G195" s="4" t="inlineStr"/>
       <c r="H195" s="4" t="inlineStr"/>
       <c r="I195" s="4" t="n">
-        <v>0.9752</v>
+        <v>0.9058</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>0.979</v>
+        <v>0.9106</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0.9571</v>
+        <v>0.9048</v>
       </c>
       <c r="L195" s="4" t="inlineStr"/>
       <c r="M195" s="4" t="inlineStr"/>
@@ -18272,7 +18402,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>RESS1G</t>
+          <t>DPNTBG1</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr"/>
@@ -18283,13 +18413,13 @@
       <c r="G196" s="4" t="inlineStr"/>
       <c r="H196" s="4" t="inlineStr"/>
       <c r="I196" s="4" t="n">
-        <v>0.9286</v>
+        <v>0.9402</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>0.9089</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0.8702</v>
+        <v>0.9048</v>
       </c>
       <c r="L196" s="4" t="inlineStr"/>
       <c r="M196" s="4" t="inlineStr"/>
@@ -18297,7 +18427,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>RIVNBG2</t>
+          <t>RESS1G</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr"/>
@@ -18308,13 +18438,13 @@
       <c r="G197" s="4" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr"/>
       <c r="I197" s="4" t="n">
-        <v>0.9058</v>
+        <v>0.9286</v>
       </c>
       <c r="J197" s="4" t="n">
-        <v>0.9106</v>
+        <v>0.9089</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>0.9048</v>
+        <v>0.8702</v>
       </c>
       <c r="L197" s="4" t="inlineStr"/>
       <c r="M197" s="4" t="inlineStr"/>
@@ -18322,69 +18452,46 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CAPBES1G</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr"/>
-      <c r="C198" s="4" t="inlineStr"/>
-      <c r="D198" s="4" t="inlineStr"/>
-      <c r="E198" s="4" t="inlineStr"/>
-      <c r="F198" s="4" t="inlineStr"/>
-      <c r="G198" s="4" t="inlineStr"/>
-      <c r="H198" s="4" t="inlineStr"/>
-      <c r="I198" s="4" t="inlineStr"/>
+          <t>WESTCBT1</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="C198" s="4" t="n">
+        <v>1.0005</v>
+      </c>
+      <c r="D198" s="4" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="F198" s="4" t="n">
+        <v>0.9973</v>
+      </c>
+      <c r="G198" s="4" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="H198" s="4" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="I198" s="4" t="n">
+        <v>0.9976</v>
+      </c>
       <c r="J198" s="4" t="n">
-        <v>0.9704</v>
+        <v>0.9958</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0.9337</v>
-      </c>
-      <c r="L198" s="4" t="inlineStr"/>
+        <v>0.9954</v>
+      </c>
+      <c r="L198" s="4" t="n">
+        <v>0.9961</v>
+      </c>
       <c r="M198" s="4" t="inlineStr"/>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>WESTCBT1</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="n">
-        <v>0.9991</v>
-      </c>
-      <c r="C199" s="4" t="n">
-        <v>1.0005</v>
-      </c>
-      <c r="D199" s="4" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="E199" s="4" t="n">
-        <v>1.0006</v>
-      </c>
-      <c r="F199" s="4" t="n">
-        <v>0.9973</v>
-      </c>
-      <c r="G199" s="4" t="n">
-        <v>0.9983</v>
-      </c>
-      <c r="H199" s="4" t="n">
-        <v>0.9987</v>
-      </c>
-      <c r="I199" s="4" t="n">
-        <v>0.9976</v>
-      </c>
-      <c r="J199" s="4" t="n">
-        <v>0.9958</v>
-      </c>
-      <c r="K199" s="4" t="n">
-        <v>0.9954</v>
-      </c>
-      <c r="L199" s="4" t="n">
-        <v>0.9961</v>
-      </c>
-      <c r="M199" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B199">
+  <conditionalFormatting sqref="B2:B198">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -18396,7 +18503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C199">
+  <conditionalFormatting sqref="C2:C198">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -18408,7 +18515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D199">
+  <conditionalFormatting sqref="D2:D198">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -18420,7 +18527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E199">
+  <conditionalFormatting sqref="E2:E198">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -18432,7 +18539,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F199">
+  <conditionalFormatting sqref="F2:F198">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -18444,7 +18551,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G199">
+  <conditionalFormatting sqref="G2:G198">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -18456,7 +18563,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H199">
+  <conditionalFormatting sqref="H2:H198">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -18468,7 +18575,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I199">
+  <conditionalFormatting sqref="I2:I198">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -18480,7 +18587,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J199">
+  <conditionalFormatting sqref="J2:J198">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -18492,7 +18599,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K199">
+  <conditionalFormatting sqref="K2:K198">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -18504,7 +18611,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L199">
+  <conditionalFormatting sqref="L2:L198">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -18516,7 +18623,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M199">
+  <conditionalFormatting sqref="M2:M198">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -18597,7 +18704,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>QPSFB1</t>
+          <t>QPSFB2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -18607,7 +18714,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -18626,12 +18733,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CRWASF1</t>
+          <t>QPSFB1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Corowa Solar Farm</t>
+          <t>Quorn Park Solar Hybrid</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -18640,85 +18747,85 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.8899</v>
+        <v>0.9032</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.9355</v>
+        <v>1.019</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.0456</v>
+        <v>-0.1158</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-4.87</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WLWLSF2</t>
+          <t>LIMBESS1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Walla Walla Solar Farm 2</t>
+          <t>Limondale Battery</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.8894</v>
+        <v>0.8568</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.9298</v>
+        <v>0.928</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-0.0404</v>
+        <v>-0.0712</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-4.35</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>WLWLSF1</t>
+          <t>BHB1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Walla Walla Solar Farm 1</t>
+          <t>Broken Hill Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.8908</v>
+        <v>0.892</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.9298</v>
+        <v>0.9484</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.039</v>
+        <v>-0.0564</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-4.19</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FINLYSF1</t>
+          <t>CRWASF1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Finley Solar Farm</t>
+          <t>Corowa Solar Farm</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -18727,27 +18834,27 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8521</v>
+        <v>0.8899</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8898</v>
+        <v>0.9355</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.0377</v>
+        <v>-0.0456</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-4.24</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CUSF1</t>
+          <t>WLWLSF2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Culcairn Solar Farm</t>
+          <t>Walla Walla Solar Farm 2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -18756,27 +18863,27 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.8903</v>
+        <v>0.8894</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9278</v>
+        <v>0.9298</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.0375</v>
+        <v>-0.0404</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-4.04</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BOMENSF1</t>
+          <t>WLWLSF1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Bomen Solar Farm</t>
+          <t>Walla Walla Solar Farm 1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -18785,56 +18892,56 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.8823</v>
+        <v>0.8908</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9187</v>
+        <v>0.9298</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.0364</v>
+        <v>-0.039</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-3.96</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>WAGGNSF1</t>
+          <t>RESS1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Wagga North Solar Farm</t>
+          <t>Riverina Energy Storage System 1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.8824</v>
+        <v>0.9008</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9183</v>
+        <v>0.9396</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.0359</v>
+        <v>-0.0388</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-3.91</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WYASF1</t>
+          <t>FINLYSF1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Wyalong Solar Farm</t>
+          <t>Finley Solar Farm</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -18843,27 +18950,27 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8865</v>
+        <v>0.8521</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.922</v>
+        <v>0.8898</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.0355</v>
+        <v>-0.0377</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-3.85</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>WSTWYSF1</t>
+          <t>CUSF1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>West Wyalong Solar Farm</t>
+          <t>Culcairn Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -18872,56 +18979,56 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8865</v>
+        <v>0.8903</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.922</v>
+        <v>0.9278</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.0355</v>
+        <v>-0.0375</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-3.85</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SEBSF1</t>
+          <t>DPNTB1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Sebastopol Solar Farm</t>
+          <t>Darlington Point Energy Storage System</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.8865</v>
+        <v>0.9085</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.922</v>
+        <v>0.9453</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.0355</v>
+        <v>-0.0368</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-3.85</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>JUNEESF1</t>
+          <t>BOMENSF1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Junee Solar Farm</t>
+          <t>Bomen Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -18930,27 +19037,27 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8865</v>
+        <v>0.8823</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.922</v>
+        <v>0.9187</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.0355</v>
+        <v>-0.0364</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-3.85</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIMOSF11</t>
+          <t>WAGGNSF1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Limondale Solar Farm 1</t>
+          <t>Wagga North Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -18959,27 +19066,27 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8206</v>
+        <v>0.8824</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8529</v>
+        <v>0.9183</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.0323</v>
+        <v>-0.0359</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-3.79</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>COLEASF1</t>
+          <t>WYASF1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Coleambally Solar Farm</t>
+          <t>Wyalong Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -18988,27 +19095,27 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8416</v>
+        <v>0.8865</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.873</v>
+        <v>0.922</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.0314</v>
+        <v>-0.0355</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-3.6</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SUNRSF1</t>
+          <t>WSTWYSF1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SUNRAYSIA SF</t>
+          <t>West Wyalong Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -19017,27 +19124,27 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8218</v>
+        <v>0.8865</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8529</v>
+        <v>0.922</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0311</v>
+        <v>-0.0355</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-3.65</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AVLSF1</t>
+          <t>SEBSF1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Avonlie Solar Farm</t>
+          <t>Sebastopol Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -19046,27 +19153,27 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8395</v>
+        <v>0.8865</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8698</v>
+        <v>0.922</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.0303</v>
+        <v>-0.0355</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-3.48</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DARLSF1</t>
+          <t>JUNEESF1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Darlington Point Solar Farm</t>
+          <t>Junee Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -19075,56 +19182,56 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8554</v>
+        <v>0.8865</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8854</v>
+        <v>0.922</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.0355</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-3.39</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GESF1</t>
+          <t>RIVNB2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Glenellen Solar Farm</t>
+          <t>Riverena Energy Storage System 2</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9102</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9255</v>
+        <v>0.9443</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.0278</v>
+        <v>-0.0341</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-3</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GRIFSF1</t>
+          <t>LIMOSF11</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Griffith Solar Farm</t>
+          <t>Limondale Solar Farm 1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -19133,27 +19240,27 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8206</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8921</v>
+        <v>0.8529</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.0267</v>
+        <v>-0.0323</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-2.99</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LIMOSF21</t>
+          <t>COLEASF1</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Limondale Solar Farm 2</t>
+          <t>Coleambally Solar Farm</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -19162,16 +19269,16 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8268</v>
+        <v>0.8416</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8528</v>
+        <v>0.873</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.026</v>
+        <v>-0.0314</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-3.05</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="25">
@@ -19250,7 +19357,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>URANQ12</t>
+          <t>URANQ11</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -19279,7 +19386,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>URANQ13</t>
+          <t>URANQ12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -19308,7 +19415,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>URANQ11</t>
+          <t>URANQ13</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -19395,99 +19502,99 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GB01</t>
+          <t>NESBESS2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Broken Hill Gas Turbines</t>
+          <t>New England BESS</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.9505</v>
+        <v>0.9197</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.9228</v>
+        <v>0.8903</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0277</v>
+        <v>0.0294</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>UPPTUMUT</t>
+          <t>NESBESS1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Tumut Power Station</t>
+          <t>New England BESS</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.967</v>
+        <v>0.9197</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.9408</v>
+        <v>0.8903</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.0262</v>
+        <v>0.0294</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>THEDROP1</t>
+          <t>GB01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>The Drop Power Station</t>
+          <t>Broken Hill Gas Turbines</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.9944</v>
+        <v>0.9505</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.9712</v>
+        <v>0.9228</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.0232</v>
+        <v>0.0277</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL3</t>
+          <t>UPPTUMUT</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Tumut 3 Power Station</t>
+          <t>Tumut Power Station</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -19496,27 +19603,27 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.9887</v>
+        <v>0.967</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.9673</v>
+        <v>0.9408</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.0214</v>
+        <v>0.0262</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL2</t>
+          <t>THEDROP1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Tumut 3 Power Station</t>
+          <t>The Drop Power Station</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -19525,27 +19632,27 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>0.9887</v>
+        <v>0.9944</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.9673</v>
+        <v>0.9712</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.0214</v>
+        <v>0.0232</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TUMT3NL1</t>
+          <t>JOUNAMA1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Tumut 3 Power Station</t>
+          <t>Jounama Small Hydro Power Station</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -19569,12 +19676,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>JOUNAMA1</t>
+          <t>TUMT3NL1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Jounama Small Hydro Power Station</t>
+          <t>Tumut 3 Power Station</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -19598,12 +19705,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BLOWERNG</t>
+          <t>TUMT3NL2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Blowering Power Station</t>
+          <t>Tumut 3 Power Station</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -19612,27 +19719,27 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.9396</v>
+        <v>0.9887</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9673</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0187</v>
+        <v>0.0214</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GUTHEGA</t>
+          <t>TUMT3NL3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Guthega Power Station</t>
+          <t>Tumut 3 Power Station</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -19641,27 +19748,27 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.9273</v>
+        <v>0.9887</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.9135</v>
+        <v>0.9673</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.0138</v>
+        <v>0.0214</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.51</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HUMENSW</t>
+          <t>BLOWERNG</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Hume (NSW) Hydro Power Station</t>
+          <t>Blowering Power Station</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -19670,56 +19777,56 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.945</v>
+        <v>0.9396</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.9316</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.0134</v>
+        <v>0.0187</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MOREESF1</t>
+          <t>GUTHEGA</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Moree Solar Farm</t>
+          <t>Guthega Power Station</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.8509</v>
+        <v>0.9273</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.8387</v>
+        <v>0.9135</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.0122</v>
+        <v>0.0138</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WYANGALB</t>
+          <t>HUMENSW</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Wyangala B Power Station</t>
+          <t>Hume (NSW) Hydro Power Station</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -19728,56 +19835,56 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0.998</v>
+        <v>0.945</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.9858</v>
+        <v>0.9316</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.0122</v>
+        <v>0.0134</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>WYANGALA</t>
+          <t>MOREESF1</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Wyangala A Power Station</t>
+          <t>Moree Solar Farm</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.998</v>
+        <v>0.8509</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.9858</v>
+        <v>0.8387</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>0.0122</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BROWNMT</t>
+          <t>WYANGALB</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Brown Mountain Hydro Power Station</t>
+          <t>Wyangala B Power Station</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -19786,16 +19893,16 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.9912</v>
+        <v>0.998</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.9792</v>
+        <v>0.9858</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.012</v>
+        <v>0.0122</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/NSW_mlf.xlsx
+++ b/outputs/NSW_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -725,27 +725,25 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>WRWF1</t>
+          <t>WRSF1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>White Rock Wind Farm</t>
+          <t>White Rock Solar Farm</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>175</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="n">
-        <v>0.8468</v>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="n">
         <v>0.8427</v>
       </c>
@@ -788,25 +786,27 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>WRSF1</t>
+          <t>WRWF1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>White Rock Solar Farm</t>
+          <t>White Rock Wind Farm</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>0.8468</v>
+      </c>
       <c r="H5" s="5" t="n">
         <v>0.8427</v>
       </c>
@@ -1860,12 +1860,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>WYASF1</t>
+          <t>WSTWYSF1</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Wyalong Solar Farm</t>
+          <t>West Wyalong Solar Farm</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
@@ -1913,12 +1913,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>WSTWYSF1</t>
+          <t>WYASF1</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>West Wyalong Solar Farm</t>
+          <t>Wyalong Solar Farm</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NEWENSF2</t>
+          <t>NEWENSF1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2223,7 +2223,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NEWENSF1</t>
+          <t>NEWENSF2</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2276,12 +2276,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GOONSF1</t>
+          <t>PARSF1</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Goonumbla Solar Farm</t>
+          <t>Parkes Solar Farm</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2290,14 +2290,18 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="n">
+        <v>1.0135</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.9964</v>
+      </c>
       <c r="I31" s="5" t="n">
-        <v>0.9791</v>
+        <v>0.9812</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>0.9258999999999999</v>
@@ -2335,12 +2339,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>PARSF1</t>
+          <t>GOONSF1</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Parkes Solar Farm</t>
+          <t>Goonumbla Solar Farm</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2349,18 +2353,14 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="n">
-        <v>1.0135</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.9964</v>
-      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.9791</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>0.9258999999999999</v>
@@ -2632,7 +2632,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>QPSFB2</t>
+          <t>QPSFB1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2642,11 +2642,11 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr"/>
@@ -2668,26 +2668,20 @@
       <c r="R37" s="5" t="n">
         <v>0.9032</v>
       </c>
-      <c r="S37" s="5" t="n">
-        <v>0.9032</v>
-      </c>
+      <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="n">
         <v>-0.1158</v>
       </c>
       <c r="U37" s="6" t="n">
         <v>-11.36</v>
       </c>
-      <c r="V37" s="5" t="n">
-        <v>-0.0144</v>
-      </c>
-      <c r="W37" s="6" t="n">
-        <v>-1.57</v>
-      </c>
+      <c r="V37" s="5" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>QPSFB1</t>
+          <t>QPSFB2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2697,11 +2691,11 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr"/>
@@ -2723,15 +2717,21 @@
       <c r="R38" s="5" t="n">
         <v>0.9032</v>
       </c>
-      <c r="S38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="n">
+        <v>0.9032</v>
+      </c>
       <c r="T38" s="5" t="n">
         <v>-0.1158</v>
       </c>
       <c r="U38" s="6" t="n">
         <v>-11.36</v>
       </c>
-      <c r="V38" s="5" t="inlineStr"/>
-      <c r="W38" s="6" t="inlineStr"/>
+      <c r="V38" s="5" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="W38" s="6" t="n">
+        <v>-1.57</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2968,7 +2968,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>URANQ13</t>
+          <t>URANQ14</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3169,7 +3169,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>URANQ14</t>
+          <t>URANQ13</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3354,51 +3354,55 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>SKSF1</t>
+          <t>GUTHEGA</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>South Keswick Solar Farm</t>
+          <t>Guthega Power Station</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.9371</v>
+      </c>
       <c r="G49" s="5" t="n">
-        <v>0.9714</v>
+        <v>0.9658</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.9708</v>
+        <v>0.9537</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.9603</v>
+        <v>0.9016</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9125</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.9444</v>
+        <v>0.9006</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.9352</v>
+        <v>0.887</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0.9439</v>
+        <v>0.893</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>0.9284</v>
+        <v>0.892</v>
       </c>
       <c r="O49" s="5" t="inlineStr"/>
       <c r="P49" s="5" t="n">
-        <v>0.923</v>
+        <v>0.9135</v>
       </c>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="n">
@@ -3406,10 +3410,10 @@
       </c>
       <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0138</v>
       </c>
       <c r="U49" s="6" t="n">
-        <v>0.47</v>
+        <v>1.51</v>
       </c>
       <c r="V49" s="5" t="inlineStr"/>
       <c r="W49" s="6" t="inlineStr"/>
@@ -3417,12 +3421,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NEVERSF1</t>
+          <t>SKSF1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Nevertire Solar Farm</t>
+          <t>South Keswick Solar Farm</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3431,14 +3435,18 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.9708</v>
+      </c>
       <c r="I50" s="5" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9603</v>
       </c>
       <c r="J50" s="5" t="n">
         <v>0.9569</v>
@@ -3476,12 +3484,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NASF1</t>
+          <t>WELLSF1</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Narromine Solar Farm</t>
+          <t xml:space="preserve">Wellington Solar Farm </t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3490,21 +3498,15 @@
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="n">
-        <v>0.9714</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>0.9708</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>0.9603</v>
-      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="K51" s="5" t="n">
         <v>0.9444</v>
@@ -3539,12 +3541,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>WELLSF1</t>
+          <t>NEVERSF1</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wellington Solar Farm </t>
+          <t>Nevertire Solar Farm</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3553,15 +3555,17 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="n">
+        <v>0.9582000000000001</v>
+      </c>
       <c r="J52" s="5" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9569</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>0.9444</v>
@@ -3596,55 +3600,51 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>GUTHEGA</t>
+          <t>NASF1</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Guthega Power Station</t>
+          <t>Narromine Solar Farm</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.8882</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.9371</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="n">
-        <v>0.9658</v>
+        <v>0.9714</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.9537</v>
+        <v>0.9708</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.9016</v>
+        <v>0.9603</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>0.9125</v>
+        <v>0.9569</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.9006</v>
+        <v>0.9444</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.887</v>
+        <v>0.9352</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.893</v>
+        <v>0.9439</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.892</v>
+        <v>0.9284</v>
       </c>
       <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="n">
-        <v>0.9135</v>
+        <v>0.923</v>
       </c>
       <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="n">
@@ -3652,10 +3652,10 @@
       </c>
       <c r="S53" s="5" t="inlineStr"/>
       <c r="T53" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0043</v>
       </c>
       <c r="U53" s="6" t="n">
-        <v>1.51</v>
+        <v>0.47</v>
       </c>
       <c r="V53" s="5" t="inlineStr"/>
       <c r="W53" s="6" t="inlineStr"/>
@@ -4446,12 +4446,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>CULLRGWF</t>
+          <t>GUNNING1</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Cullerin Range Wind Farm</t>
+          <t>Gunning Wind Farm</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>30</v>
+        <v>46.5</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>0.9742</v>
@@ -4513,12 +4513,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>GUNNING1</t>
+          <t>CULLRGWF</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Gunning Wind Farm</t>
+          <t>Cullerin Range Wind Farm</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>46.5</v>
+        <v>30</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>0.9742</v>
@@ -4621,7 +4621,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>HUNTER2</t>
+          <t>HUNTER1</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>HUNTER1</t>
+          <t>HUNTER2</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -6075,12 +6075,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>WOODLWN1</t>
+          <t>CAPTL_WF</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Woodlawn Wind Farm</t>
+          <t>Capital Wind Farm</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6089,7 +6089,7 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>48.3</v>
+        <v>140</v>
       </c>
       <c r="E94" s="5" t="n">
         <v>0.9748</v>
@@ -6142,12 +6142,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>CAPTL_WF</t>
+          <t>WOODLWN1</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Capital Wind Farm</t>
+          <t>Woodlawn Wind Farm</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>140</v>
+        <v>48.3</v>
       </c>
       <c r="E95" s="5" t="n">
         <v>0.9748</v>
@@ -6276,21 +6276,21 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>NYNGAN1</t>
+          <t>BDONGHYD</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Nyngan Solar Plant</t>
+          <t>Burrendong Hydro Power Station</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>102.141</v>
+        <v>19</v>
       </c>
       <c r="E97" s="5" t="n">
         <v>0.9903</v>
@@ -6343,21 +6343,21 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>BDONGHYD</t>
+          <t>NYNGAN1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Burrendong Hydro Power Station</t>
+          <t>Nyngan Solar Plant</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>19</v>
+        <v>102.141</v>
       </c>
       <c r="E98" s="5" t="n">
         <v>0.9903</v>
@@ -6542,7 +6542,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>MP1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -6609,7 +6609,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MP1</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -6676,21 +6676,21 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>GLBWNHYD</t>
+          <t>GLENNCRK</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Glenbawn Hydro Power Station</t>
+          <t>Glennies Creek Power Station</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>5.5</v>
+        <v>12.78</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>0.9828</v>
@@ -6743,21 +6743,21 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>GLENNCRK</t>
+          <t>GLBWNHYD</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Glennies Creek Power Station</t>
+          <t>Glenbawn Hydro Power Station</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>12.78</v>
+        <v>5.5</v>
       </c>
       <c r="E104" s="5" t="n">
         <v>0.9828</v>
@@ -6869,17 +6869,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-1</t>
+          <t>TUMUT2-4</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1</t>
+          <t>TUMUT2</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr"/>
       <c r="D106" s="4" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E106" s="5" t="n">
         <v>0.9768</v>
@@ -6932,17 +6932,17 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-2</t>
+          <t>TUMUT2-1</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1</t>
+          <t>TUMUT2</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr"/>
       <c r="D107" s="4" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E107" s="5" t="n">
         <v>0.9768</v>
@@ -6995,7 +6995,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-3</t>
+          <t>TUMUT1-4</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7058,7 +7058,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2-4</t>
+          <t>TUMUT2-3</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7184,17 +7184,17 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2-1</t>
+          <t>TUMUT1-3</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2</t>
+          <t>TUMUT1</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr"/>
       <c r="D111" s="4" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E111" s="5" t="n">
         <v>0.9768</v>
@@ -7247,7 +7247,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-4</t>
+          <t>TUMUT1-1</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7310,17 +7310,17 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2-3</t>
+          <t>TUMUT1-2</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2</t>
+          <t>TUMUT1</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr"/>
       <c r="D113" s="4" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E113" s="5" t="n">
         <v>0.9768</v>
@@ -7499,8 +7499,14 @@
           <t>Eraring Battery Energy Storage System</t>
         </is>
       </c>
-      <c r="C116" s="3" t="n"/>
-      <c r="D116" s="3" t="inlineStr"/>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>614.6</v>
+      </c>
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr"/>
@@ -7544,7 +7550,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>CG3</t>
+          <t>CG1</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -7611,7 +7617,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>CG2</t>
+          <t>CG3</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -7678,7 +7684,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>CG4</t>
+          <t>CG2</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -7745,7 +7751,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>CG1</t>
+          <t>CG4</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -7871,7 +7877,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>ERGT01</t>
+          <t>ER01</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -7885,7 +7891,7 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>41.5</v>
+        <v>720</v>
       </c>
       <c r="E122" s="5" t="n">
         <v>0.9856</v>
@@ -7938,7 +7944,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>ER02</t>
+          <t>ERGT01</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -7952,7 +7958,7 @@
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>720</v>
+        <v>41.5</v>
       </c>
       <c r="E123" s="5" t="n">
         <v>0.9856</v>
@@ -8005,7 +8011,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>ER01</t>
+          <t>ER02</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8446,7 +8452,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>VP6</t>
+          <t>VP5</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -8513,7 +8519,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>VPNL1</t>
+          <t>VP6</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8527,7 +8533,7 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>25</v>
+        <v>660</v>
       </c>
       <c r="E132" s="5" t="n">
         <v>0.9877</v>
@@ -8580,7 +8586,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>VP5</t>
+          <t>VPNL1</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -8594,7 +8600,7 @@
         </is>
       </c>
       <c r="D133" s="4" t="n">
-        <v>660</v>
+        <v>25</v>
       </c>
       <c r="E133" s="5" t="n">
         <v>0.9877</v>
@@ -8714,7 +8720,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL1</t>
+          <t>TUMT3NL2</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -8781,7 +8787,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL2</t>
+          <t>TUMT3NL3</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -8848,7 +8854,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL3</t>
+          <t>TUMT3NL1</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9653,12 +9659,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>WYANGALB</t>
+          <t>WYANGALA</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Wyangala B Power Station</t>
+          <t>Wyangala A Power Station</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -9667,7 +9673,7 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E150" s="5" t="n">
         <v>1.0099</v>
@@ -9720,12 +9726,12 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>WYANGALA</t>
+          <t>WYANGALB</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Wyangala A Power Station</t>
+          <t>Wyangala B Power Station</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -9734,7 +9740,7 @@
         </is>
       </c>
       <c r="D151" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5" t="n">
         <v>1.0099</v>
@@ -9787,7 +9793,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>LUCAS2S2</t>
+          <t>LUCASHGT</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -9801,7 +9807,7 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>4.6</v>
+        <v>12.65</v>
       </c>
       <c r="E152" s="5" t="n">
         <v>1.0016</v>
@@ -9854,7 +9860,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>LUCASHGT</t>
+          <t>LUCAS2S2</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -9868,7 +9874,7 @@
         </is>
       </c>
       <c r="D153" s="4" t="n">
-        <v>12.65</v>
+        <v>4.6</v>
       </c>
       <c r="E153" s="5" t="n">
         <v>1.0016</v>
@@ -10319,12 +10325,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>EASTCRK</t>
+          <t>EASTCRK2</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Eastern Creek LFG PS Units 1-4</t>
+          <t>Eastern Creek 2 Gas Utilisation Facility</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -10333,22 +10339,22 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>5.056</v>
+        <v>6.738</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1.0018</v>
+        <v>1.0021</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>1.0035</v>
+        <v>1.0021</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1.0041</v>
+        <v>1.0021</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>1.0033</v>
+        <v>1.0021</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>1.001</v>
+        <v>1.0021</v>
       </c>
       <c r="J160" s="5" t="n">
         <v>1.001</v>
@@ -10386,12 +10392,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>EASTCRK2</t>
+          <t>EASTCRK</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Eastern Creek 2 Gas Utilisation Facility</t>
+          <t>Eastern Creek LFG PS Units 1-4</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -10400,22 +10406,22 @@
         </is>
       </c>
       <c r="D161" s="4" t="n">
-        <v>6.738</v>
+        <v>5.056</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0018</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0035</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0041</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0033</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.001</v>
       </c>
       <c r="J161" s="5" t="n">
         <v>1.001</v>
@@ -10634,21 +10640,21 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>TARALGA1</t>
+          <t>WDLNGN01</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Taralga Wind Farm</t>
+          <t>Woodlawn Bioreactor Energy Generation Station</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D165" s="4" t="n">
-        <v>106.8</v>
+        <v>7</v>
       </c>
       <c r="E165" s="5" t="n">
         <v>0.9844000000000001</v>
@@ -10701,21 +10707,21 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>WDLNGN01</t>
+          <t>TARALGA1</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Woodlawn Bioreactor Energy Generation Station</t>
+          <t>Taralga Wind Farm</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>7</v>
+        <v>106.8</v>
       </c>
       <c r="E166" s="5" t="n">
         <v>0.9844000000000001</v>
@@ -10886,7 +10892,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-4</t>
+          <t>TUMUT3-6</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10949,7 +10955,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-3</t>
+          <t>TUMUT3-5</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11012,7 +11018,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-5</t>
+          <t>TUMUT3-4</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -11075,7 +11081,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-1</t>
+          <t>TUMUT3-2</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -11138,7 +11144,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-2</t>
+          <t>TUMUT3-3</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -11201,7 +11207,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-6</t>
+          <t>TUMUT3-1</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -11487,42 +11493,38 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>TERALBA</t>
+          <t>HVGTS</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>TERALBA POWER STATION</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="n">
-        <v>3</v>
-      </c>
+          <t>Hunter Valley Gas Turbine</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D180" s="3" t="inlineStr"/>
       <c r="E180" s="5" t="n">
-        <v>0.9926</v>
+        <v>0.974</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9679</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.9892</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="H180" s="5" t="n">
-        <v>0.9901</v>
+        <v>0.9596</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9654</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9673</v>
       </c>
       <c r="K180" s="5" t="n">
-        <v>0.9917</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="L180" s="5" t="inlineStr"/>
       <c r="M180" s="5" t="inlineStr"/>
@@ -11540,12 +11542,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>WOYWOY1</t>
+          <t>KINCUM1</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Woy Woy Landfill Site</t>
+          <t>Kincumber Landfill Site</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -11593,38 +11595,42 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>HVGTS</t>
+          <t>AGLNOW1</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Hunter Valley Gas Turbine</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D182" s="3" t="inlineStr"/>
+          <t>West Nowra Landfill Gas Power Generation Facility</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E182" s="5" t="n">
-        <v>0.974</v>
+        <v>0.9916</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>0.9679</v>
+        <v>0.9986</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9582000000000001</v>
+        <v>1.0023</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.9596</v>
+        <v>1.0037</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.9654</v>
+        <v>0.9929</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.9673</v>
+        <v>0.9967</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="L182" s="5" t="inlineStr"/>
       <c r="M182" s="5" t="inlineStr"/>
@@ -11693,42 +11699,42 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>AGLNOW1</t>
+          <t>LD03</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>West Nowra Landfill Gas Power Generation Facility</t>
+          <t>Liddell Power Station</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0.9916</v>
+        <v>0.9676</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.9986</v>
+        <v>0.9593</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>1.0023</v>
+        <v>0.9509</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>1.0037</v>
+        <v>0.9537</v>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9593</v>
       </c>
       <c r="J184" s="5" t="n">
-        <v>0.9967</v>
+        <v>0.9631</v>
       </c>
       <c r="K184" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9628</v>
       </c>
       <c r="L184" s="5" t="inlineStr"/>
       <c r="M184" s="5" t="inlineStr"/>
@@ -11746,12 +11752,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>KINCUM1</t>
+          <t>TERALBA</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Kincumber Landfill Site</t>
+          <t>TERALBA POWER STATION</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -11760,28 +11766,28 @@
         </is>
       </c>
       <c r="D185" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1.0017</v>
+        <v>0.9926</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>1.0015</v>
+        <v>0.9907</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>1.0008</v>
+        <v>0.9892</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>1.0011</v>
+        <v>0.9901</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="J185" s="5" t="n">
-        <v>1.0019</v>
+        <v>0.9907</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>1.0037</v>
+        <v>0.9917</v>
       </c>
       <c r="L185" s="5" t="inlineStr"/>
       <c r="M185" s="5" t="inlineStr"/>
@@ -11799,42 +11805,42 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>LD03</t>
+          <t>WOYWOY1</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Liddell Power Station</t>
+          <t>Woy Woy Landfill Site</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.9676</v>
+        <v>1.0017</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.9593</v>
+        <v>1.0015</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.9509</v>
+        <v>1.0008</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>0.9537</v>
+        <v>1.0011</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>0.9593</v>
+        <v>1.0036</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>0.9631</v>
+        <v>1.0019</v>
       </c>
       <c r="K186" s="5" t="n">
-        <v>0.9628</v>
+        <v>1.0037</v>
       </c>
       <c r="L186" s="5" t="inlineStr"/>
       <c r="M186" s="5" t="inlineStr"/>
@@ -11907,7 +11913,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>LD02</t>
+          <t>LD01</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -11962,7 +11968,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>LD01</t>
+          <t>LD02</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -12017,21 +12023,21 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>WALGRVG1</t>
+          <t>MLLFGEF1</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Wallgrove BESS 1</t>
+          <t>Mugga Lane Landfill Gas To Energy Facility</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E190" s="5" t="inlineStr"/>
       <c r="F190" s="5" t="inlineStr"/>
@@ -12040,16 +12046,16 @@
       <c r="I190" s="5" t="inlineStr"/>
       <c r="J190" s="5" t="inlineStr"/>
       <c r="K190" s="5" t="n">
-        <v>1.0011</v>
+        <v>0.9683</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>1.001</v>
+        <v>0.9687</v>
       </c>
       <c r="M190" s="5" t="n">
-        <v>1.001</v>
+        <v>0.9663</v>
       </c>
       <c r="N190" s="5" t="n">
-        <v>1.001</v>
+        <v>0.9567</v>
       </c>
       <c r="O190" s="5" t="inlineStr"/>
       <c r="P190" s="5" t="inlineStr"/>
@@ -12064,21 +12070,21 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>MLLFGEF1</t>
+          <t>DPNTBG1</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Mugga Lane Landfill Gas To Energy Facility</t>
+          <t>Darlington Point Energy Storage System</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D191" s="4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E191" s="5" t="inlineStr"/>
       <c r="F191" s="5" t="inlineStr"/>
@@ -12086,17 +12092,15 @@
       <c r="H191" s="5" t="inlineStr"/>
       <c r="I191" s="5" t="inlineStr"/>
       <c r="J191" s="5" t="inlineStr"/>
-      <c r="K191" s="5" t="n">
-        <v>0.9683</v>
-      </c>
+      <c r="K191" s="5" t="inlineStr"/>
       <c r="L191" s="5" t="n">
-        <v>0.9687</v>
+        <v>0.9402</v>
       </c>
       <c r="M191" s="5" t="n">
-        <v>0.9663</v>
+        <v>0.9089</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>0.9567</v>
+        <v>0.9048</v>
       </c>
       <c r="O191" s="5" t="inlineStr"/>
       <c r="P191" s="5" t="inlineStr"/>
@@ -12111,12 +12115,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>BHBG1</t>
+          <t>RESS1G</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Broken Hill Battery Energy Storage System</t>
+          <t>Riverina BESS 1</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -12125,7 +12129,7 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E192" s="5" t="inlineStr"/>
       <c r="F192" s="5" t="inlineStr"/>
@@ -12134,12 +12138,14 @@
       <c r="I192" s="5" t="inlineStr"/>
       <c r="J192" s="5" t="inlineStr"/>
       <c r="K192" s="5" t="inlineStr"/>
-      <c r="L192" s="5" t="inlineStr"/>
+      <c r="L192" s="5" t="n">
+        <v>0.9286</v>
+      </c>
       <c r="M192" s="5" t="n">
-        <v>0.8671</v>
+        <v>0.9089</v>
       </c>
       <c r="N192" s="5" t="n">
-        <v>0.8423</v>
+        <v>0.8702</v>
       </c>
       <c r="O192" s="5" t="inlineStr"/>
       <c r="P192" s="5" t="inlineStr"/>
@@ -12154,12 +12160,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>CAPBES1G</t>
+          <t>RIVNBG2</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Capital Battery</t>
+          <t>Riverina Energy Storage System 2</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -12168,7 +12174,7 @@
         </is>
       </c>
       <c r="D193" s="4" t="n">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="E193" s="5" t="inlineStr"/>
       <c r="F193" s="5" t="inlineStr"/>
@@ -12177,12 +12183,14 @@
       <c r="I193" s="5" t="inlineStr"/>
       <c r="J193" s="5" t="inlineStr"/>
       <c r="K193" s="5" t="inlineStr"/>
-      <c r="L193" s="5" t="inlineStr"/>
+      <c r="L193" s="5" t="n">
+        <v>0.9058</v>
+      </c>
       <c r="M193" s="5" t="n">
-        <v>0.9704</v>
+        <v>0.9106</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>0.9337</v>
+        <v>0.9048</v>
       </c>
       <c r="O193" s="5" t="inlineStr"/>
       <c r="P193" s="5" t="inlineStr"/>
@@ -12197,12 +12205,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>QBYNBG1</t>
+          <t>WALGRVG1</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Queanbeyan BESS</t>
+          <t>Wallgrove BESS 1</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -12211,7 +12219,7 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E194" s="5" t="inlineStr"/>
       <c r="F194" s="5" t="inlineStr"/>
@@ -12219,15 +12227,17 @@
       <c r="H194" s="5" t="inlineStr"/>
       <c r="I194" s="5" t="inlineStr"/>
       <c r="J194" s="5" t="inlineStr"/>
-      <c r="K194" s="5" t="inlineStr"/>
+      <c r="K194" s="5" t="n">
+        <v>1.0011</v>
+      </c>
       <c r="L194" s="5" t="n">
-        <v>0.9752</v>
+        <v>1.001</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>0.979</v>
+        <v>1.001</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>0.9571</v>
+        <v>1.001</v>
       </c>
       <c r="O194" s="5" t="inlineStr"/>
       <c r="P194" s="5" t="inlineStr"/>
@@ -12242,12 +12252,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>RIVNBG2</t>
+          <t>BHBG1</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Riverina Energy Storage System 2</t>
+          <t>Broken Hill Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -12256,7 +12266,7 @@
         </is>
       </c>
       <c r="D195" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E195" s="5" t="inlineStr"/>
       <c r="F195" s="5" t="inlineStr"/>
@@ -12265,14 +12275,12 @@
       <c r="I195" s="5" t="inlineStr"/>
       <c r="J195" s="5" t="inlineStr"/>
       <c r="K195" s="5" t="inlineStr"/>
-      <c r="L195" s="5" t="n">
-        <v>0.9058</v>
-      </c>
+      <c r="L195" s="5" t="inlineStr"/>
       <c r="M195" s="5" t="n">
-        <v>0.9106</v>
+        <v>0.8671</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>0.9048</v>
+        <v>0.8423</v>
       </c>
       <c r="O195" s="5" t="inlineStr"/>
       <c r="P195" s="5" t="inlineStr"/>
@@ -12287,12 +12295,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>DPNTBG1</t>
+          <t>QBYNBG1</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Darlington Point Energy Storage System</t>
+          <t>Queanbeyan BESS</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -12301,7 +12309,7 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E196" s="5" t="inlineStr"/>
       <c r="F196" s="5" t="inlineStr"/>
@@ -12311,13 +12319,13 @@
       <c r="J196" s="5" t="inlineStr"/>
       <c r="K196" s="5" t="inlineStr"/>
       <c r="L196" s="5" t="n">
-        <v>0.9402</v>
+        <v>0.9752</v>
       </c>
       <c r="M196" s="5" t="n">
-        <v>0.9089</v>
+        <v>0.979</v>
       </c>
       <c r="N196" s="5" t="n">
-        <v>0.9048</v>
+        <v>0.9571</v>
       </c>
       <c r="O196" s="5" t="inlineStr"/>
       <c r="P196" s="5" t="inlineStr"/>
@@ -12332,12 +12340,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>RESS1G</t>
+          <t>CAPBES1G</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Riverina BESS 1</t>
+          <t>Capital Battery</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -12346,7 +12354,7 @@
         </is>
       </c>
       <c r="D197" s="4" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E197" s="5" t="inlineStr"/>
       <c r="F197" s="5" t="inlineStr"/>
@@ -12355,14 +12363,12 @@
       <c r="I197" s="5" t="inlineStr"/>
       <c r="J197" s="5" t="inlineStr"/>
       <c r="K197" s="5" t="inlineStr"/>
-      <c r="L197" s="5" t="n">
-        <v>0.9286</v>
-      </c>
+      <c r="L197" s="5" t="inlineStr"/>
       <c r="M197" s="5" t="n">
-        <v>0.9089</v>
+        <v>0.9704</v>
       </c>
       <c r="N197" s="5" t="n">
-        <v>0.8702</v>
+        <v>0.9337</v>
       </c>
       <c r="O197" s="5" t="inlineStr"/>
       <c r="P197" s="5" t="inlineStr"/>
@@ -12626,14 +12632,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>WRWF1</t>
+          <t>WRSF1</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="n">
-        <v>0.8468</v>
-      </c>
+      <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="n">
         <v>0.8427</v>
       </c>
@@ -12668,12 +12672,14 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>WRSF1</t>
+          <t>WRWF1</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.8468</v>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.8427</v>
       </c>
@@ -13362,7 +13368,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>WYASF1</t>
+          <t>WSTWYSF1</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
@@ -13394,7 +13400,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>WSTWYSF1</t>
+          <t>WYASF1</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr"/>
@@ -13546,7 +13552,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NEWENSF2</t>
+          <t>NEWENSF1</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr"/>
@@ -13578,7 +13584,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NEWENSF1</t>
+          <t>NEWENSF2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
@@ -13610,15 +13616,19 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GOONSF1</t>
+          <t>PARSF1</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="n">
+        <v>1.0135</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.9964</v>
+      </c>
       <c r="F31" s="5" t="n">
-        <v>0.9791</v>
+        <v>0.9812</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0.9258999999999999</v>
@@ -13648,19 +13658,15 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>PARSF1</t>
+          <t>GOONSF1</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="n">
-        <v>1.0135</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>0.9964</v>
-      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="5" t="n">
-        <v>0.9812</v>
+        <v>0.9791</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0.9258999999999999</v>
@@ -13840,7 +13846,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>QPSFB2</t>
+          <t>QPSFB1</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr"/>
@@ -13863,14 +13869,12 @@
       <c r="O37" s="5" t="n">
         <v>0.9032</v>
       </c>
-      <c r="P37" s="5" t="n">
-        <v>0.9032</v>
-      </c>
+      <c r="P37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>QPSFB1</t>
+          <t>QPSFB2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr"/>
@@ -13893,7 +13897,9 @@
       <c r="O38" s="5" t="n">
         <v>0.9032</v>
       </c>
-      <c r="P38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="n">
+        <v>0.9032</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -14038,7 +14044,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>URANQ13</t>
+          <t>URANQ14</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -14176,7 +14182,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>URANQ14</t>
+          <t>URANQ13</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -14298,38 +14304,42 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>SKSF1</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="5" t="inlineStr"/>
+          <t>GUTHEGA</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.8882</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.9371</v>
+      </c>
       <c r="D49" s="5" t="n">
-        <v>0.9714</v>
+        <v>0.9658</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.9708</v>
+        <v>0.9537</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.9603</v>
+        <v>0.9016</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9125</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.9444</v>
+        <v>0.9006</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.9352</v>
+        <v>0.887</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>0.9439</v>
+        <v>0.893</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.9284</v>
+        <v>0.892</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="n">
-        <v>0.923</v>
+        <v>0.9135</v>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
       <c r="O49" s="5" t="n">
@@ -14340,15 +14350,19 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NEVERSF1</t>
+          <t>SKSF1</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr"/>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.9708</v>
+      </c>
       <c r="F50" s="5" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9603</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>0.9569</v>
@@ -14378,22 +14392,16 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NASF1</t>
+          <t>WELLSF1</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr"/>
-      <c r="D51" s="5" t="n">
-        <v>0.9714</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0.9708</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0.9603</v>
-      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="n">
-        <v>0.9569</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0.9444</v>
@@ -14420,16 +14428,18 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>WELLSF1</t>
+          <t>NEVERSF1</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr"/>
       <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>0.9582000000000001</v>
+      </c>
       <c r="G52" s="5" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9569</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>0.9444</v>
@@ -14456,42 +14466,38 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>GUTHEGA</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>0.8882</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>0.9371</v>
-      </c>
+          <t>NASF1</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="5" t="n">
-        <v>0.9658</v>
+        <v>0.9714</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.9537</v>
+        <v>0.9708</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.9016</v>
+        <v>0.9603</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.9125</v>
+        <v>0.9569</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.9006</v>
+        <v>0.9444</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.887</v>
+        <v>0.9352</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>0.893</v>
+        <v>0.9439</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.892</v>
+        <v>0.9284</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="n">
-        <v>0.9135</v>
+        <v>0.923</v>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="5" t="n">
@@ -15008,7 +15014,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>CULLRGWF</t>
+          <t>GUNNING1</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -15054,7 +15060,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>GUNNING1</t>
+          <t>CULLRGWF</t>
         </is>
       </c>
       <c r="B68" s="5" t="n">
@@ -15124,7 +15130,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>HUNTER2</t>
+          <t>HUNTER1</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr"/>
@@ -15152,7 +15158,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>HUNTER1</t>
+          <t>HUNTER2</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
@@ -16066,7 +16072,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>WOODLWN1</t>
+          <t>CAPTL_WF</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -16112,7 +16118,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>CAPTL_WF</t>
+          <t>WOODLWN1</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -16204,7 +16210,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>NYNGAN1</t>
+          <t>BDONGHYD</t>
         </is>
       </c>
       <c r="B97" s="5" t="n">
@@ -16250,7 +16256,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>BDONGHYD</t>
+          <t>NYNGAN1</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -16386,7 +16392,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MP2</t>
+          <t>MP1</t>
         </is>
       </c>
       <c r="B101" s="5" t="n">
@@ -16432,7 +16438,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MP1</t>
+          <t>MP2</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -16478,7 +16484,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>GLBWNHYD</t>
+          <t>GLENNCRK</t>
         </is>
       </c>
       <c r="B103" s="5" t="n">
@@ -16524,7 +16530,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>GLENNCRK</t>
+          <t>GLBWNHYD</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -16604,7 +16610,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-1</t>
+          <t>TUMUT2-4</t>
         </is>
       </c>
       <c r="B106" s="5" t="n">
@@ -16650,7 +16656,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-2</t>
+          <t>TUMUT2-1</t>
         </is>
       </c>
       <c r="B107" s="5" t="n">
@@ -16696,7 +16702,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-3</t>
+          <t>TUMUT1-4</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
@@ -16742,7 +16748,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2-4</t>
+          <t>TUMUT2-3</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
@@ -16834,7 +16840,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2-1</t>
+          <t>TUMUT1-3</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
@@ -16880,7 +16886,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>TUMUT1-4</t>
+          <t>TUMUT1-1</t>
         </is>
       </c>
       <c r="B112" s="5" t="n">
@@ -16926,7 +16932,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TUMUT2-3</t>
+          <t>TUMUT1-2</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
@@ -17074,7 +17080,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>CG3</t>
+          <t>CG1</t>
         </is>
       </c>
       <c r="B117" s="5" t="n">
@@ -17120,7 +17126,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>CG2</t>
+          <t>CG3</t>
         </is>
       </c>
       <c r="B118" s="5" t="n">
@@ -17166,7 +17172,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>CG4</t>
+          <t>CG2</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
@@ -17212,7 +17218,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>CG1</t>
+          <t>CG4</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
@@ -17292,7 +17298,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>ERGT01</t>
+          <t>ER01</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
@@ -17338,7 +17344,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>ER02</t>
+          <t>ERGT01</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
@@ -17384,7 +17390,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>ER01</t>
+          <t>ER02</t>
         </is>
       </c>
       <c r="B124" s="5" t="n">
@@ -17670,7 +17676,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>VP6</t>
+          <t>VP5</t>
         </is>
       </c>
       <c r="B131" s="5" t="n">
@@ -17716,7 +17722,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>VPNL1</t>
+          <t>VP6</t>
         </is>
       </c>
       <c r="B132" s="5" t="n">
@@ -17762,7 +17768,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>VP5</t>
+          <t>VPNL1</t>
         </is>
       </c>
       <c r="B133" s="5" t="n">
@@ -17854,7 +17860,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL1</t>
+          <t>TUMT3NL2</t>
         </is>
       </c>
       <c r="B135" s="5" t="n">
@@ -17900,7 +17906,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL2</t>
+          <t>TUMT3NL3</t>
         </is>
       </c>
       <c r="B136" s="5" t="n">
@@ -17946,7 +17952,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL3</t>
+          <t>TUMT3NL1</t>
         </is>
       </c>
       <c r="B137" s="5" t="n">
@@ -18478,7 +18484,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>WYANGALB</t>
+          <t>WYANGALA</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
@@ -18524,7 +18530,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>WYANGALA</t>
+          <t>WYANGALB</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
@@ -18570,7 +18576,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>LUCAS2S2</t>
+          <t>LUCASHGT</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
@@ -18616,7 +18622,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>LUCASHGT</t>
+          <t>LUCAS2S2</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
@@ -18938,23 +18944,23 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>EASTCRK</t>
+          <t>EASTCRK2</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>1.0018</v>
+        <v>1.0021</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>1.0035</v>
+        <v>1.0021</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>1.0041</v>
+        <v>1.0021</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1.0033</v>
+        <v>1.0021</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>1.001</v>
+        <v>1.0021</v>
       </c>
       <c r="G160" s="5" t="n">
         <v>1.001</v>
@@ -18984,23 +18990,23 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>EASTCRK2</t>
+          <t>EASTCRK</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0018</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0035</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0041</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.0033</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>1.0021</v>
+        <v>1.001</v>
       </c>
       <c r="G161" s="5" t="n">
         <v>1.001</v>
@@ -19140,7 +19146,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>TARALGA1</t>
+          <t>WDLNGN01</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
@@ -19186,7 +19192,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>WDLNGN01</t>
+          <t>TARALGA1</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
@@ -19308,7 +19314,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-4</t>
+          <t>TUMUT3-6</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
@@ -19354,7 +19360,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-3</t>
+          <t>TUMUT3-5</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
@@ -19400,7 +19406,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-5</t>
+          <t>TUMUT3-4</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
@@ -19446,7 +19452,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-1</t>
+          <t>TUMUT3-2</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
@@ -19492,7 +19498,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-2</t>
+          <t>TUMUT3-3</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
@@ -19538,7 +19544,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>TUMUT3-6</t>
+          <t>TUMUT3-1</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
@@ -19726,29 +19732,29 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>TERALBA</t>
+          <t>HVGTS</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>0.9926</v>
+        <v>0.974</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9679</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>0.9892</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>0.9901</v>
+        <v>0.9596</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9654</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.9907</v>
+        <v>0.9673</v>
       </c>
       <c r="H180" s="5" t="n">
-        <v>0.9917</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="I180" s="5" t="inlineStr"/>
       <c r="J180" s="5" t="inlineStr"/>
@@ -19762,7 +19768,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>WOYWOY1</t>
+          <t>KINCUM1</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
@@ -19798,29 +19804,29 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>HVGTS</t>
+          <t>AGLNOW1</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>0.974</v>
+        <v>0.9916</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>0.9679</v>
+        <v>0.9986</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>0.9582000000000001</v>
+        <v>1.0023</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>0.9596</v>
+        <v>1.0037</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>0.9654</v>
+        <v>0.9929</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.9673</v>
+        <v>0.9967</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="I182" s="5" t="inlineStr"/>
       <c r="J182" s="5" t="inlineStr"/>
@@ -19868,29 +19874,29 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>AGLNOW1</t>
+          <t>LD03</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>0.9916</v>
+        <v>0.9676</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>0.9986</v>
+        <v>0.9593</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>1.0023</v>
+        <v>0.9509</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1.0037</v>
+        <v>0.9537</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9593</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.9967</v>
+        <v>0.9631</v>
       </c>
       <c r="H184" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9628</v>
       </c>
       <c r="I184" s="5" t="inlineStr"/>
       <c r="J184" s="5" t="inlineStr"/>
@@ -19904,29 +19910,29 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>KINCUM1</t>
+          <t>TERALBA</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
-        <v>1.0017</v>
+        <v>0.9926</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>1.0015</v>
+        <v>0.9907</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>1.0008</v>
+        <v>0.9892</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1.0011</v>
+        <v>0.9901</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>1.0019</v>
+        <v>0.9907</v>
       </c>
       <c r="H185" s="5" t="n">
-        <v>1.0037</v>
+        <v>0.9917</v>
       </c>
       <c r="I185" s="5" t="inlineStr"/>
       <c r="J185" s="5" t="inlineStr"/>
@@ -19940,29 +19946,29 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>LD03</t>
+          <t>WOYWOY1</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
-        <v>0.9676</v>
+        <v>1.0017</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>0.9593</v>
+        <v>1.0015</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>0.9509</v>
+        <v>1.0008</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.9537</v>
+        <v>1.0011</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.9593</v>
+        <v>1.0036</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>0.9631</v>
+        <v>1.0019</v>
       </c>
       <c r="H186" s="5" t="n">
-        <v>0.9628</v>
+        <v>1.0037</v>
       </c>
       <c r="I186" s="5" t="inlineStr"/>
       <c r="J186" s="5" t="inlineStr"/>
@@ -20014,7 +20020,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>LD02</t>
+          <t>LD01</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
@@ -20052,7 +20058,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>LD01</t>
+          <t>LD02</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
@@ -20090,7 +20096,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>WALGRVG1</t>
+          <t>MLLFGEF1</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr"/>
@@ -20100,16 +20106,16 @@
       <c r="F190" s="5" t="inlineStr"/>
       <c r="G190" s="5" t="inlineStr"/>
       <c r="H190" s="5" t="n">
-        <v>1.0011</v>
+        <v>0.9683</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>1.001</v>
+        <v>0.9687</v>
       </c>
       <c r="J190" s="5" t="n">
-        <v>1.001</v>
+        <v>0.9663</v>
       </c>
       <c r="K190" s="5" t="n">
-        <v>1.001</v>
+        <v>0.9567</v>
       </c>
       <c r="L190" s="5" t="inlineStr"/>
       <c r="M190" s="5" t="inlineStr"/>
@@ -20120,7 +20126,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>MLLFGEF1</t>
+          <t>DPNTBG1</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr"/>
@@ -20129,17 +20135,15 @@
       <c r="E191" s="5" t="inlineStr"/>
       <c r="F191" s="5" t="inlineStr"/>
       <c r="G191" s="5" t="inlineStr"/>
-      <c r="H191" s="5" t="n">
-        <v>0.9683</v>
-      </c>
+      <c r="H191" s="5" t="inlineStr"/>
       <c r="I191" s="5" t="n">
-        <v>0.9687</v>
+        <v>0.9402</v>
       </c>
       <c r="J191" s="5" t="n">
-        <v>0.9663</v>
+        <v>0.9089</v>
       </c>
       <c r="K191" s="5" t="n">
-        <v>0.9567</v>
+        <v>0.9048</v>
       </c>
       <c r="L191" s="5" t="inlineStr"/>
       <c r="M191" s="5" t="inlineStr"/>
@@ -20150,7 +20154,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>BHBG1</t>
+          <t>RESS1G</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr"/>
@@ -20160,12 +20164,14 @@
       <c r="F192" s="5" t="inlineStr"/>
       <c r="G192" s="5" t="inlineStr"/>
       <c r="H192" s="5" t="inlineStr"/>
-      <c r="I192" s="5" t="inlineStr"/>
+      <c r="I192" s="5" t="n">
+        <v>0.9286</v>
+      </c>
       <c r="J192" s="5" t="n">
-        <v>0.8671</v>
+        <v>0.9089</v>
       </c>
       <c r="K192" s="5" t="n">
-        <v>0.8423</v>
+        <v>0.8702</v>
       </c>
       <c r="L192" s="5" t="inlineStr"/>
       <c r="M192" s="5" t="inlineStr"/>
@@ -20176,7 +20182,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>CAPBES1G</t>
+          <t>RIVNBG2</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr"/>
@@ -20186,12 +20192,14 @@
       <c r="F193" s="5" t="inlineStr"/>
       <c r="G193" s="5" t="inlineStr"/>
       <c r="H193" s="5" t="inlineStr"/>
-      <c r="I193" s="5" t="inlineStr"/>
+      <c r="I193" s="5" t="n">
+        <v>0.9058</v>
+      </c>
       <c r="J193" s="5" t="n">
-        <v>0.9704</v>
+        <v>0.9106</v>
       </c>
       <c r="K193" s="5" t="n">
-        <v>0.9337</v>
+        <v>0.9048</v>
       </c>
       <c r="L193" s="5" t="inlineStr"/>
       <c r="M193" s="5" t="inlineStr"/>
@@ -20202,7 +20210,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>QBYNBG1</t>
+          <t>WALGRVG1</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr"/>
@@ -20211,15 +20219,17 @@
       <c r="E194" s="5" t="inlineStr"/>
       <c r="F194" s="5" t="inlineStr"/>
       <c r="G194" s="5" t="inlineStr"/>
-      <c r="H194" s="5" t="inlineStr"/>
+      <c r="H194" s="5" t="n">
+        <v>1.0011</v>
+      </c>
       <c r="I194" s="5" t="n">
-        <v>0.9752</v>
+        <v>1.001</v>
       </c>
       <c r="J194" s="5" t="n">
-        <v>0.979</v>
+        <v>1.001</v>
       </c>
       <c r="K194" s="5" t="n">
-        <v>0.9571</v>
+        <v>1.001</v>
       </c>
       <c r="L194" s="5" t="inlineStr"/>
       <c r="M194" s="5" t="inlineStr"/>
@@ -20230,7 +20240,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>RIVNBG2</t>
+          <t>BHBG1</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr"/>
@@ -20240,14 +20250,12 @@
       <c r="F195" s="5" t="inlineStr"/>
       <c r="G195" s="5" t="inlineStr"/>
       <c r="H195" s="5" t="inlineStr"/>
-      <c r="I195" s="5" t="n">
-        <v>0.9058</v>
-      </c>
+      <c r="I195" s="5" t="inlineStr"/>
       <c r="J195" s="5" t="n">
-        <v>0.9106</v>
+        <v>0.8671</v>
       </c>
       <c r="K195" s="5" t="n">
-        <v>0.9048</v>
+        <v>0.8423</v>
       </c>
       <c r="L195" s="5" t="inlineStr"/>
       <c r="M195" s="5" t="inlineStr"/>
@@ -20258,7 +20266,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>DPNTBG1</t>
+          <t>QBYNBG1</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr"/>
@@ -20269,13 +20277,13 @@
       <c r="G196" s="5" t="inlineStr"/>
       <c r="H196" s="5" t="inlineStr"/>
       <c r="I196" s="5" t="n">
-        <v>0.9402</v>
+        <v>0.9752</v>
       </c>
       <c r="J196" s="5" t="n">
-        <v>0.9089</v>
+        <v>0.979</v>
       </c>
       <c r="K196" s="5" t="n">
-        <v>0.9048</v>
+        <v>0.9571</v>
       </c>
       <c r="L196" s="5" t="inlineStr"/>
       <c r="M196" s="5" t="inlineStr"/>
@@ -20286,7 +20294,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>RESS1G</t>
+          <t>CAPBES1G</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr"/>
@@ -20296,14 +20304,12 @@
       <c r="F197" s="5" t="inlineStr"/>
       <c r="G197" s="5" t="inlineStr"/>
       <c r="H197" s="5" t="inlineStr"/>
-      <c r="I197" s="5" t="n">
-        <v>0.9286</v>
-      </c>
+      <c r="I197" s="5" t="inlineStr"/>
       <c r="J197" s="5" t="n">
-        <v>0.9089</v>
+        <v>0.9704</v>
       </c>
       <c r="K197" s="5" t="n">
-        <v>0.8702</v>
+        <v>0.9337</v>
       </c>
       <c r="L197" s="5" t="inlineStr"/>
       <c r="M197" s="5" t="inlineStr"/>
@@ -20605,7 +20611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>QPSFB2</t>
+          <t>QPSFB1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -20615,7 +20621,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
@@ -20634,7 +20640,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>QPSFB1</t>
+          <t>QPSFB2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -20644,7 +20650,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -20895,12 +20901,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>WYASF1</t>
+          <t>JUNEESF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Wyalong Solar Farm</t>
+          <t>Junee Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -20924,12 +20930,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>WSTWYSF1</t>
+          <t>SEBSF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>West Wyalong Solar Farm</t>
+          <t>Sebastopol Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -20953,12 +20959,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SEBSF1</t>
+          <t>WSTWYSF1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Sebastopol Solar Farm</t>
+          <t>West Wyalong Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -20982,12 +20988,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>JUNEESF1</t>
+          <t>WYASF1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Junee Solar Farm</t>
+          <t>Wyalong Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -21258,7 +21264,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>URANQ11</t>
+          <t>URANQ12</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -21287,7 +21293,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>URANQ12</t>
+          <t>URANQ11</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -21664,7 +21670,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL1</t>
+          <t>TUMT3NL2</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -21693,7 +21699,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL2</t>
+          <t>TUMT3NL3</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -21722,7 +21728,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TUMT3NL3</t>
+          <t>TUMT3NL1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
